--- a/data/preseason2026/2026-2027 TPBL 季前熱身賽球員數據表 - 新北中信特攻.xlsx
+++ b/data/preseason2026/2026-2027 TPBL 季前熱身賽球員數據表 - 新北中信特攻.xlsx
@@ -5,8 +5,8 @@
   <sheets>
     <sheet state="visible" name="平均數據" sheetId="1" r:id="rId5"/>
     <sheet state="visible" name="球員進階數據 (Advanced Stats)" sheetId="2" r:id="rId6"/>
-    <sheet state="visible" name="2026.10.09 G01 vs 高雄全家海神" sheetId="3" r:id="rId7"/>
-    <sheet state="visible" name="2026.10.10 G02 vs 福爾摩沙夢想家" sheetId="4" r:id="rId8"/>
+    <sheet state="visible" name="2026.10.09 G01 海神 vs 特攻" sheetId="3" r:id="rId7"/>
+    <sheet state="visible" name="2026.10.10 G05 夢想家 vs 特攻" sheetId="4" r:id="rId8"/>
   </sheets>
   <definedNames/>
   <calcPr/>
@@ -19,6 +19,12 @@
     <t>2026-2027 賽季 新北中信特攻 (TPBL) 球員進階數據統計表 (USG%, TS%, GmSc 等)</t>
   </si>
   <si>
+    <t>2026-2027 賽季 新北中信特攻 (TPBL) 季前熱身賽球員攻守數據與進階陣容分析表 (全2戰累積版)</t>
+  </si>
+  <si>
+    <t>註：採計TPBL 2026-2027 季前熱身賽官方電子紀錄攻守數據。數據包含傳統攻守、進階指標及 PBP 無換人時間段陣容分析。</t>
+  </si>
+  <si>
     <t>球隊</t>
   </si>
   <si>
@@ -37,21 +43,33 @@
     <t>出賽</t>
   </si>
   <si>
+    <t>本土/洋將</t>
+  </si>
+  <si>
     <t>上場時間</t>
   </si>
   <si>
     <t>場均得分</t>
   </si>
   <si>
+    <t>在台年資</t>
+  </si>
+  <si>
     <t>投籃命中</t>
   </si>
   <si>
     <t>投籃出手</t>
   </si>
   <si>
+    <t>時間[分]</t>
+  </si>
+  <si>
     <t>命中%</t>
   </si>
   <si>
+    <t>得分</t>
+  </si>
+  <si>
     <t>三分命中</t>
   </si>
   <si>
@@ -61,18 +79,24 @@
     <t>三分%</t>
   </si>
   <si>
-    <t>2026-2027 賽季 新北中信特攻 (TPBL) 季前熱身賽球員攻守數據與進階陣容分析表 (全2戰累積版)</t>
-  </si>
-  <si>
     <t>罰球命中</t>
   </si>
   <si>
+    <t>兩分命中</t>
+  </si>
+  <si>
     <t>罰球出手</t>
   </si>
   <si>
+    <t>兩分出手</t>
+  </si>
+  <si>
     <t>罰球%</t>
   </si>
   <si>
+    <t>兩分%</t>
+  </si>
+  <si>
     <t>eFG%</t>
   </si>
   <si>
@@ -91,21 +115,45 @@
     <t>AST%</t>
   </si>
   <si>
-    <t>註：採計TPBL 2026-2027 季前熱身賽官方電子紀錄攻守數據。數據包含傳統攻守、進階指標及 PBP 無換人時間段陣容分析。</t>
-  </si>
-  <si>
     <t>TOV%</t>
   </si>
   <si>
+    <t>進攻籃板</t>
+  </si>
+  <si>
     <t>GmSc</t>
   </si>
   <si>
+    <t>防守籃板</t>
+  </si>
+  <si>
     <t>AST/TO</t>
   </si>
   <si>
+    <t>籃板</t>
+  </si>
+  <si>
+    <t>助攻</t>
+  </si>
+  <si>
+    <t>抄截</t>
+  </si>
+  <si>
     <t>新北中信特攻</t>
   </si>
   <si>
+    <t>阻攻</t>
+  </si>
+  <si>
+    <t>失誤</t>
+  </si>
+  <si>
+    <t>犯規</t>
+  </si>
+  <si>
+    <t>EFF</t>
+  </si>
+  <si>
     <t>猛士 (Clay Mounce)</t>
   </si>
   <si>
@@ -115,27 +163,6 @@
     <t>F</t>
   </si>
   <si>
-    <t>本土/洋將</t>
-  </si>
-  <si>
-    <t>在台年資</t>
-  </si>
-  <si>
-    <t>時間[分]</t>
-  </si>
-  <si>
-    <t>得分</t>
-  </si>
-  <si>
-    <t>兩分命中</t>
-  </si>
-  <si>
-    <t>兩分出手</t>
-  </si>
-  <si>
-    <t>兩分%</t>
-  </si>
-  <si>
     <t>謝亞軒 (Hsieh Ya-Hsuan)</t>
   </si>
   <si>
@@ -145,145 +172,172 @@
     <t>SG</t>
   </si>
   <si>
-    <t>進攻籃板</t>
-  </si>
-  <si>
-    <t>防守籃板</t>
-  </si>
-  <si>
-    <t>籃板</t>
-  </si>
-  <si>
-    <t>助攻</t>
-  </si>
-  <si>
-    <t>抄截</t>
-  </si>
-  <si>
-    <t>阻攻</t>
-  </si>
-  <si>
     <t>奈迪 (Ndiaye)</t>
   </si>
   <si>
+    <t>投籃熱區與進攻特徵分佈</t>
+  </si>
+  <si>
     <t>C</t>
   </si>
   <si>
-    <t>失誤</t>
-  </si>
-  <si>
-    <t>犯規</t>
-  </si>
-  <si>
-    <t>EFF</t>
+    <t>備註 / 熱身賽表現重點</t>
+  </si>
+  <si>
+    <t>累計在場時間</t>
+  </si>
+  <si>
+    <t>累計On_ORtg</t>
+  </si>
+  <si>
+    <t>累計On_DRtg</t>
+  </si>
+  <si>
+    <t>累計On_NetRtg</t>
+  </si>
+  <si>
+    <t>累計Off_NetRtg</t>
+  </si>
+  <si>
+    <t>賽季淨影響力(Diff)</t>
   </si>
   <si>
     <t>法拉帝 (Farr)</t>
   </si>
   <si>
+    <t>五人陣容組合</t>
+  </si>
+  <si>
+    <t>賽季累計時間</t>
+  </si>
+  <si>
+    <t>累計正負值(+/-)</t>
+  </si>
+  <si>
+    <t>Lineup ORtg</t>
+  </si>
+  <si>
+    <t>Lineup DRtg</t>
+  </si>
+  <si>
+    <t>Lineup NetRtg</t>
+  </si>
+  <si>
+    <t>洋將搭檔組合</t>
+  </si>
+  <si>
+    <t>共同時間</t>
+  </si>
+  <si>
+    <t>累計(+/-)</t>
+  </si>
+  <si>
+    <t>攻守特徵與搭配建議</t>
+  </si>
+  <si>
     <t>魏嘉豪 (Wei Chia-Hao)</t>
   </si>
   <si>
     <t>PG</t>
   </si>
   <si>
-    <t>投籃熱區與進攻特徵分佈</t>
-  </si>
-  <si>
-    <t>備註 / 熱身賽表現重點</t>
+    <t>第1年</t>
   </si>
   <si>
     <t>阿巴西 (Mohammad Al Bachir Gadiaga)</t>
   </si>
   <si>
-    <t>累計在場時間</t>
-  </si>
-  <si>
-    <t>累計On_ORtg</t>
-  </si>
-  <si>
-    <t>累計On_DRtg</t>
-  </si>
-  <si>
-    <t>累計On_NetRtg</t>
-  </si>
-  <si>
-    <t>累計Off_NetRtg</t>
-  </si>
-  <si>
-    <t>賽季淨影響力(Diff)</t>
-  </si>
-  <si>
-    <t>五人陣容組合</t>
-  </si>
-  <si>
-    <t>賽季累計時間</t>
+    <t>2026-2027 賽季 新北中信特攻 (TPBL) 季前熱身賽單場球員攻守數據表 (136 : 133 勝(OT) 高雄全家海神)</t>
   </si>
   <si>
     <t>黃泓瀚 (Huang Hung-Han)</t>
   </si>
   <si>
-    <t>累計正負值(+/-)</t>
-  </si>
-  <si>
     <t>SF</t>
   </si>
   <si>
-    <t>Lineup ORtg</t>
-  </si>
-  <si>
-    <t>Lineup DRtg</t>
-  </si>
-  <si>
-    <t>Lineup NetRtg</t>
-  </si>
-  <si>
-    <t>洋將搭檔組合</t>
-  </si>
-  <si>
-    <t>共同時間</t>
-  </si>
-  <si>
-    <t>累計(+/-)</t>
-  </si>
-  <si>
-    <t>攻守特徵與搭配建議</t>
+    <t>註：採計TPBL 2026-2027 季前熱身賽官方電子紀錄攻守數據。比賽日期：2026年10月09日，地點：和平籃球館。</t>
+  </si>
+  <si>
+    <t>2026-2027 賽季 新北中信特攻 (TPBL) 季前熱身賽單場球員攻守數據表 (92 : 97 負 福爾摩沙夢想家)</t>
+  </si>
+  <si>
+    <t>註：採計TPBL 2026-2027 季前熱身賽官方電子紀錄攻守數據。比賽日期：2026年10月10日，地點：和平籃球館。</t>
   </si>
   <si>
     <t>劉人豪 (Liu Jen-Hao)</t>
   </si>
   <si>
-    <t>第1年</t>
+    <t>內外兼修(兩分67% / 三分33%)</t>
+  </si>
+  <si>
+    <t>兩戰狂轟50分18籃板4抄截，外線命中率46.2%，全能大前鋒</t>
   </si>
   <si>
     <t>曾文鼎 (Tseng Wen-Ting)</t>
   </si>
   <si>
+    <t>猛士</t>
+  </si>
+  <si>
     <t>李睿麒 (Lee Ruei-Ci)</t>
   </si>
   <si>
+    <t>魏嘉豪-謝亞軒-黃泓瀚-猛士-法拉帝</t>
+  </si>
+  <si>
+    <t>+/-</t>
+  </si>
+  <si>
+    <t>備註 / 單場表現重點</t>
+  </si>
+  <si>
     <t>周承睿 (Chou Cheng-Jui)</t>
   </si>
   <si>
+    <t>時間</t>
+  </si>
+  <si>
+    <t>On_ORtg</t>
+  </si>
+  <si>
     <t>PF</t>
   </si>
   <si>
+    <t>On_DRtg</t>
+  </si>
+  <si>
+    <t>猛士 + 法拉帝 (內外攻守均衡配)</t>
+  </si>
+  <si>
+    <t>On_NetRtg</t>
+  </si>
+  <si>
+    <t>Off_NetRtg</t>
+  </si>
+  <si>
+    <t>Diff</t>
+  </si>
+  <si>
+    <t>正負值(+/-)</t>
+  </si>
+  <si>
     <t>陳冠全 (Chen Kuan-Chuan)</t>
   </si>
   <si>
-    <t>2026-2027 賽季 新北中信特攻 (TPBL) 季前熱身賽單場球員攻守數據表 (92 : 97 負 福爾摩沙夢想家)</t>
+    <t>對位情境</t>
+  </si>
+  <si>
+    <t>表現與影響</t>
+  </si>
+  <si>
+    <t>猛士具備外線與單打能力，法拉帝高位策應與內線護框，攻防默契最佳</t>
   </si>
   <si>
     <t>李學林 (Lee Hsueh-Lin)</t>
   </si>
   <si>
-    <t>註：採計TPBL 2026-2027 季前熱身賽官方電子紀錄攻守數據。比賽日期：2026年10月10日，地點：和平籃球館。</t>
-  </si>
-  <si>
-    <t>內外兼修(兩分67% / 三分33%)</t>
-  </si>
-  <si>
-    <t>兩戰狂轟50分18籃板4抄截，外線命中率46.2%，全能大前鋒</t>
+    <t>5年</t>
   </si>
   <si>
     <t>余維豪 (Yu Wei-Hao)</t>
@@ -292,54 +346,6 @@
     <t>G</t>
   </si>
   <si>
-    <t>猛士</t>
-  </si>
-  <si>
-    <t>魏嘉豪-謝亞軒-黃泓瀚-猛士-法拉帝</t>
-  </si>
-  <si>
-    <t>猛士 + 法拉帝 (內外攻守均衡配)</t>
-  </si>
-  <si>
-    <t>+/-</t>
-  </si>
-  <si>
-    <t>備註 / 單場表現重點</t>
-  </si>
-  <si>
-    <t>猛士具備外線與單打能力，法拉帝高位策應與內線護框，攻防默契最佳</t>
-  </si>
-  <si>
-    <t>時間</t>
-  </si>
-  <si>
-    <t>5年</t>
-  </si>
-  <si>
-    <t>On_ORtg</t>
-  </si>
-  <si>
-    <t>On_DRtg</t>
-  </si>
-  <si>
-    <t>On_NetRtg</t>
-  </si>
-  <si>
-    <t>Off_NetRtg</t>
-  </si>
-  <si>
-    <t>Diff</t>
-  </si>
-  <si>
-    <t>正負值(+/-)</t>
-  </si>
-  <si>
-    <t>對位情境</t>
-  </si>
-  <si>
-    <t>表現與影響</t>
-  </si>
-  <si>
     <t>外線投射為主(三分佔比73%)</t>
   </si>
   <si>
@@ -349,52 +355,103 @@
     <t>謝亞軒</t>
   </si>
   <si>
+    <t>外線砲火</t>
+  </si>
+  <si>
+    <t>三分球10投7中狂轟27分4抄截3助攻，射手本色盡顯，正負值+18</t>
+  </si>
+  <si>
+    <t>全能輸出</t>
+  </si>
+  <si>
+    <t>法拉帝</t>
+  </si>
+  <si>
+    <t>狂轟全場最高28分命中6記三分，外加4籃板3助攻3抄截2阻攻，EFF 34</t>
+  </si>
+  <si>
+    <t>簡廷兆</t>
+  </si>
+  <si>
     <t>劉人豪-謝亞軒-阿巴西-猛士-法拉帝</t>
   </si>
   <si>
+    <t>魏嘉豪-謝亞軒-阿巴西-猛士-法拉帝</t>
+  </si>
+  <si>
     <t>猛士 + 奈迪 (鋒線機動火力組合)</t>
   </si>
   <si>
-    <t>全能輸出</t>
-  </si>
-  <si>
-    <t>狂轟全場最高28分命中6記三分，外加4籃板3助攻3抄截2阻攻，EFF 34</t>
-  </si>
-  <si>
-    <t>簡廷兆</t>
-  </si>
-  <si>
     <t>外線砲火猛烈，但防守籃板保護較單薄，需本土長人補位</t>
   </si>
   <si>
+    <t>謝亞軒在場對位于煥亞 (32:35)</t>
+  </si>
+  <si>
+    <t>于煥亞三分 6 投 2 中得 6 分，謝亞軒三分 10 投 7 中飆 27 分完全宰制外線</t>
+  </si>
+  <si>
+    <t>猛士在場對位霍爾曼 (31:13)</t>
+  </si>
+  <si>
+    <t>霍爾曼得 14 分 9 籃板，猛士以 6 記三分狂轟 28 分佔據優勢</t>
+  </si>
+  <si>
+    <t>奈迪 (Nedim)</t>
+  </si>
+  <si>
+    <t>全能前鋒</t>
+  </si>
+  <si>
     <t>內外兼修</t>
   </si>
   <si>
+    <t>兩分球14投10中攻下22分8籃板2助攻，正負值+13</t>
+  </si>
+  <si>
     <t>得分爆發力強，但失誤與犯規偏多需控制</t>
   </si>
   <si>
     <t>魏嘉豪</t>
   </si>
   <si>
-    <t>魏嘉豪-謝亞軒-阿巴西-猛士-法拉帝</t>
+    <t>簡廷兆-謝亞軒-阿巴西-猛士-法拉帝</t>
   </si>
   <si>
     <t>魏嘉豪-謝亞軒-阿巴西-奈迪-法拉帝</t>
   </si>
   <si>
+    <t>謝亞軒下場休息 (20:25)</t>
+  </si>
+  <si>
     <t>法拉帝 + 奈迪 (雙塔內線組合)</t>
   </si>
   <si>
+    <t>特攻外線由簡廷兆接棒命中 4 記三分維持火力</t>
+  </si>
+  <si>
+    <t>罰球6罰全中攻下16分4籃板，外線命中2記三分</t>
+  </si>
+  <si>
+    <t>阿巴西</t>
+  </si>
+  <si>
+    <t>強斯 (Marvin Jones)</t>
+  </si>
+  <si>
     <t>禁區高度足夠，但外圍防守輪轉交代較慢，易遭對手三分針對</t>
   </si>
   <si>
-    <t>猛士在場對位霍爾曼 (31:13)</t>
-  </si>
-  <si>
-    <t>霍爾曼得 14 分 9 籃板，猛士以 6 記三分狂轟 28 分佔據優勢</t>
-  </si>
-  <si>
-    <t>奈迪 (Nedim)</t>
+    <t>PF/C</t>
+  </si>
+  <si>
+    <t>簡廷兆-謝亞軒-林任鴻-猛士-強斯</t>
+  </si>
+  <si>
+    <t>禁區苦工</t>
+  </si>
+  <si>
+    <t>罰球5罰全中攻下15分4籃板2助攻0失誤</t>
   </si>
   <si>
     <t>禁區強攻為主</t>
@@ -406,25 +463,28 @@
     <t>黃泓瀚</t>
   </si>
   <si>
-    <t>罰球6罰全中攻下16分4籃板，外線命中2記三分</t>
-  </si>
-  <si>
-    <t>阿巴西</t>
-  </si>
-  <si>
-    <t>簡廷兆-謝亞軒-林任鴻-猛士-強斯</t>
-  </si>
-  <si>
     <t>猛士下場休息 (16:47)</t>
   </si>
   <si>
     <t>特攻次節進攻當機長達數分鐘，單節僅拿 10 分遭夢想家逼近</t>
   </si>
   <si>
-    <t>強斯 (Marvin Jones)</t>
-  </si>
-  <si>
-    <t>PF/C</t>
+    <t>魏嘉豪-簡廷兆-阿巴西-奈迪-強斯</t>
+  </si>
+  <si>
+    <t>單場戰術結論</t>
+  </si>
+  <si>
+    <t>歐系團隊導傳體系火力全開，謝亞軒7記三分射垮海神，法拉帝統治禁區搶下19籃板，延長賽險勝。</t>
+  </si>
+  <si>
+    <t>禁區防守</t>
+  </si>
+  <si>
+    <t>貢獻13分9籃板1阻攻，罰球6罰5中</t>
+  </si>
+  <si>
+    <t>飆進2記三分攻下15分2助攻，但出現6次失誤5犯</t>
   </si>
   <si>
     <t>突破與外線並重</t>
@@ -436,43 +496,37 @@
     <t>劉人豪</t>
   </si>
   <si>
-    <t>禁區防守</t>
-  </si>
-  <si>
-    <t>貢獻13分9籃板1阻攻，罰球6罰5中</t>
-  </si>
-  <si>
     <t>魏嘉豪-謝亞軒-曾文鼎-奈迪-強斯</t>
   </si>
   <si>
-    <t>單場戰術結論</t>
+    <t>法拉帝 (Vladimír Brodziansky)</t>
   </si>
   <si>
     <t>背靠背作戰體能下滑致使次節當機僅得10分，猛士末節連飆外線難挽狂瀾，以5分差惜敗。</t>
   </si>
   <si>
-    <t>法拉帝 (Vladimír Brodziansky)</t>
-  </si>
-  <si>
-    <t>外線砲火</t>
-  </si>
-  <si>
     <t>飆進3記三分抓下11籃板完成雙十，得12分</t>
   </si>
   <si>
+    <t>籃板怪獸</t>
+  </si>
+  <si>
     <t>奈迪</t>
   </si>
   <si>
+    <t>狂抓19籃板(5前板)繳14分5助攻2抄截1阻攻，正負值+21為全場最高</t>
+  </si>
+  <si>
     <t>突破為主</t>
   </si>
   <si>
+    <t>黑豹出賽調節體能，攻防轉換箭頭</t>
+  </si>
+  <si>
     <t>F/SF</t>
   </si>
   <si>
-    <t>黑豹出賽調節體能，攻防轉換箭頭</t>
-  </si>
-  <si>
-    <t>法拉帝</t>
+    <t>9年</t>
   </si>
   <si>
     <t>轉換快攻</t>
@@ -481,12 +535,21 @@
     <t>貢獻8分7籃板4助攻1抄截，正負值+5</t>
   </si>
   <si>
-    <t>9年</t>
-  </si>
-  <si>
     <t>強斯</t>
   </si>
   <si>
+    <t>全能鋒線串聯攻防，外線空檔把握高</t>
+  </si>
+  <si>
+    <t>曾文鼎</t>
+  </si>
+  <si>
+    <t>全能箭頭</t>
+  </si>
+  <si>
+    <t>出賽近41分鐘貢獻13分8籃板6助攻2抄截，正負值+14</t>
+  </si>
+  <si>
     <t>外線輪替</t>
   </si>
   <si>
@@ -496,13 +559,16 @@
     <t>簡廷兆 (Jian Ting-Jhao)</t>
   </si>
   <si>
-    <t>全能鋒線串聯攻防，外線空檔把握高</t>
-  </si>
-  <si>
     <t>2年</t>
   </si>
   <si>
-    <t>曾文鼎</t>
+    <t>7年</t>
+  </si>
+  <si>
+    <t>外線奇兵</t>
+  </si>
+  <si>
+    <t>三分球6投4中射進12分4助攻2抄截</t>
   </si>
   <si>
     <t>替補控球</t>
@@ -511,7 +577,10 @@
     <t>替補登場送出3次助攻抓1籃板，得5分，正負值+8</t>
   </si>
   <si>
-    <t>7年</t>
+    <t>外圍組織</t>
+  </si>
+  <si>
+    <t>替補控衛掌控節奏，傳球失誤比佳</t>
   </si>
   <si>
     <t>G/PG</t>
@@ -523,30 +592,30 @@
     <t>先發控球狂送全隊最高9次助攻4籃板，僅1次失誤</t>
   </si>
   <si>
-    <t>外圍組織</t>
-  </si>
-  <si>
-    <t>替補控衛掌控節奏，傳球失誤比佳</t>
-  </si>
-  <si>
     <t>林任鴻 (Lin Jen-Hung)</t>
   </si>
   <si>
+    <t>先發控球</t>
+  </si>
+  <si>
+    <t>先發掌控傳導送出6次助攻2抄截得7分，正負值+17</t>
+  </si>
+  <si>
     <t>8年</t>
   </si>
   <si>
     <t>22年</t>
   </si>
   <si>
+    <t>李沛澄 (Li Pei-Cheng)</t>
+  </si>
+  <si>
     <t>側翼防守</t>
   </si>
   <si>
     <t>替補出賽貢獻2分，正負值+8</t>
   </si>
   <si>
-    <t>李沛澄 (Li Pei-Cheng)</t>
-  </si>
-  <si>
     <t>弧頂策應</t>
   </si>
   <si>
@@ -559,6 +628,9 @@
     <t>替補登場3分鐘</t>
   </si>
   <si>
+    <t>替補2投全中得5分</t>
+  </si>
+  <si>
     <t>6年</t>
   </si>
   <si>
@@ -568,13 +640,22 @@
     <t>大房東替補登場抓1籃板</t>
   </si>
   <si>
+    <t>大房東策應</t>
+  </si>
+  <si>
+    <t>李睿麒 (Li Ruei-Ci)</t>
+  </si>
+  <si>
+    <t>替補登場抓下4籃板攻下4分</t>
+  </si>
+  <si>
     <t>外線射手</t>
   </si>
   <si>
     <t>側翼替補登場提供防守與外線</t>
   </si>
   <si>
-    <t>李睿麒 (Li Ruei-Ci)</t>
+    <t>曾信武 (Tseng Hsin-Wu)</t>
   </si>
   <si>
     <t>防守替補</t>
@@ -583,54 +664,72 @@
     <t>替補抓1籃板</t>
   </si>
   <si>
-    <t>曾信武 (Tseng Hsin-Wu)</t>
-  </si>
-  <si>
-    <t>禁區苦工</t>
+    <t>新秀登場</t>
+  </si>
+  <si>
+    <t>替補出場1投1中得2分，正負值+11</t>
+  </si>
+  <si>
+    <t>未出賽</t>
+  </si>
+  <si>
+    <t>DNP / 本場未登錄出賽</t>
   </si>
   <si>
     <t>年輕長人登場肉搏卡位</t>
   </si>
   <si>
-    <t>未出賽</t>
-  </si>
-  <si>
-    <t>DNP / 本場未登錄出賽</t>
+    <t>側翼替補</t>
+  </si>
+  <si>
+    <t>替補登場送出1助攻</t>
+  </si>
+  <si>
+    <t>團隊總計</t>
+  </si>
+  <si>
+    <t>14名球員</t>
+  </si>
+  <si>
+    <t>―</t>
   </si>
   <si>
     <t>12年</t>
   </si>
   <si>
+    <t>團隊單場統計</t>
+  </si>
+  <si>
+    <t>次節僅得10分陷入苦戰，猛士飆進6記三分獨攬28分，但下半場遭夢想家逆轉惜敗</t>
+  </si>
+  <si>
+    <t>替補登場調節體能</t>
+  </si>
+  <si>
     <t>厚重中鋒</t>
   </si>
   <si>
     <t>老將替補登場頂防</t>
   </si>
   <si>
-    <t>團隊總計</t>
-  </si>
-  <si>
-    <t>14名球員</t>
-  </si>
-  <si>
-    <t>―</t>
+    <t>後衛替補</t>
+  </si>
+  <si>
+    <t>替補登場送出1抄截</t>
   </si>
   <si>
     <t>20年</t>
   </si>
   <si>
-    <t>團隊單場統計</t>
-  </si>
-  <si>
     <t>資深控球</t>
   </si>
   <si>
-    <t>次節僅得10分陷入苦戰，猛士飆進6記三分獨攬28分，但下半場遭夢想家逆轉惜敗</t>
-  </si>
-  <si>
     <t>老將後衛替補登場控球</t>
   </si>
   <si>
+    <t>全隊命中17記三分球，謝亞軒狂轟7記三分27分，法拉帝19籃板，延長血戰險勝海神</t>
+  </si>
+  <si>
     <t>新秀後衛</t>
   </si>
   <si>
@@ -641,105 +740,6 @@
   </si>
   <si>
     <t>熱身賽1勝1敗，百回合進攻效率108.8，防守效率109.8，淨效率-1.0</t>
-  </si>
-  <si>
-    <t>2026-2027 賽季 新北中信特攻 (TPBL) 季前熱身賽單場球員攻守數據表 (136 : 133 勝(OT) 高雄全家海神)</t>
-  </si>
-  <si>
-    <t>註：採計TPBL 2026-2027 季前熱身賽官方電子紀錄攻守數據。比賽日期：2026年10月09日，地點：和平籃球館。</t>
-  </si>
-  <si>
-    <t>三分球10投7中狂轟27分4抄截3助攻，射手本色盡顯，正負值+18</t>
-  </si>
-  <si>
-    <t>謝亞軒在場對位于煥亞 (32:35)</t>
-  </si>
-  <si>
-    <t>于煥亞三分 6 投 2 中得 6 分，謝亞軒三分 10 投 7 中飆 27 分完全宰制外線</t>
-  </si>
-  <si>
-    <t>全能前鋒</t>
-  </si>
-  <si>
-    <t>兩分球14投10中攻下22分8籃板2助攻，正負值+13</t>
-  </si>
-  <si>
-    <t>簡廷兆-謝亞軒-阿巴西-猛士-法拉帝</t>
-  </si>
-  <si>
-    <t>謝亞軒下場休息 (20:25)</t>
-  </si>
-  <si>
-    <t>特攻外線由簡廷兆接棒命中 4 記三分維持火力</t>
-  </si>
-  <si>
-    <t>罰球5罰全中攻下15分4籃板2助攻0失誤</t>
-  </si>
-  <si>
-    <t>魏嘉豪-簡廷兆-阿巴西-奈迪-強斯</t>
-  </si>
-  <si>
-    <t>歐系團隊導傳體系火力全開，謝亞軒7記三分射垮海神，法拉帝統治禁區搶下19籃板，延長賽險勝。</t>
-  </si>
-  <si>
-    <t>飆進2記三分攻下15分2助攻，但出現6次失誤5犯</t>
-  </si>
-  <si>
-    <t>籃板怪獸</t>
-  </si>
-  <si>
-    <t>狂抓19籃板(5前板)繳14分5助攻2抄截1阻攻，正負值+21為全場最高</t>
-  </si>
-  <si>
-    <t>全能箭頭</t>
-  </si>
-  <si>
-    <t>出賽近41分鐘貢獻13分8籃板6助攻2抄截，正負值+14</t>
-  </si>
-  <si>
-    <t>外線奇兵</t>
-  </si>
-  <si>
-    <t>三分球6投4中射進12分4助攻2抄截</t>
-  </si>
-  <si>
-    <t>先發控球</t>
-  </si>
-  <si>
-    <t>先發掌控傳導送出6次助攻2抄截得7分，正負值+17</t>
-  </si>
-  <si>
-    <t>替補2投全中得5分</t>
-  </si>
-  <si>
-    <t>大房東策應</t>
-  </si>
-  <si>
-    <t>替補登場抓下4籃板攻下4分</t>
-  </si>
-  <si>
-    <t>新秀登場</t>
-  </si>
-  <si>
-    <t>替補出場1投1中得2分，正負值+11</t>
-  </si>
-  <si>
-    <t>側翼替補</t>
-  </si>
-  <si>
-    <t>替補登場送出1助攻</t>
-  </si>
-  <si>
-    <t>替補登場調節體能</t>
-  </si>
-  <si>
-    <t>後衛替補</t>
-  </si>
-  <si>
-    <t>替補登場送出1抄截</t>
-  </si>
-  <si>
-    <t>全隊命中17記三分球，謝亞軒狂轟7記三分27分，法拉帝19籃板，延長血戰險勝海神</t>
   </si>
 </sst>
 </file>
@@ -830,24 +830,24 @@
     <xf borderId="1" fillId="0" fontId="3" numFmtId="164" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment readingOrder="0"/>
     </xf>
-    <xf borderId="1" fillId="0" fontId="3" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyFont="1"/>
-    <xf borderId="1" fillId="0" fontId="3" numFmtId="10" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
-      <alignment readingOrder="0"/>
-    </xf>
     <xf borderId="1" fillId="2" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="10" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
-      <alignment readingOrder="0"/>
+    <xf borderId="1" fillId="0" fontId="3" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyFont="1"/>
+    <xf quotePrefix="1" borderId="1" fillId="2" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0"/>
     </xf>
     <xf borderId="1" fillId="0" fontId="3" numFmtId="165" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment readingOrder="0"/>
     </xf>
-    <xf quotePrefix="1" borderId="1" fillId="2" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0"/>
+    <xf borderId="1" fillId="0" fontId="3" numFmtId="166" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+      <alignment readingOrder="0"/>
     </xf>
-    <xf borderId="1" fillId="0" fontId="3" numFmtId="166" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+    <xf borderId="1" fillId="0" fontId="3" numFmtId="10" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+      <alignment readingOrder="0"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="1" numFmtId="10" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
       <alignment readingOrder="0"/>
     </xf>
   </cellXfs>
@@ -876,6 +876,16 @@
       <font/>
       <fill>
         <patternFill patternType="solid">
+          <fgColor rgb="FFF3F3F3"/>
+          <bgColor rgb="FFF3F3F3"/>
+        </patternFill>
+      </fill>
+      <border/>
+    </dxf>
+    <dxf>
+      <font/>
+      <fill>
+        <patternFill patternType="solid">
           <fgColor rgb="FF003366"/>
           <bgColor rgb="FF003366"/>
         </patternFill>
@@ -886,8 +896,8 @@
       <font/>
       <fill>
         <patternFill patternType="solid">
-          <fgColor rgb="FFF3F3F3"/>
-          <bgColor rgb="FFF3F3F3"/>
+          <fgColor rgb="FFE7E8ED"/>
+          <bgColor rgb="FFE7E8ED"/>
         </patternFill>
       </fill>
       <border/>
@@ -902,82 +912,72 @@
       </fill>
       <border/>
     </dxf>
-    <dxf>
-      <font/>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFE7E8ED"/>
-          <bgColor rgb="FFE7E8ED"/>
-        </patternFill>
-      </fill>
-      <border/>
-    </dxf>
   </dxfs>
   <tableStyles count="13">
     <tableStyle count="3" pivot="0" name="球員進階數據 (Advanced Stats)-style">
       <tableStyleElement dxfId="1" type="headerRow"/>
-      <tableStyleElement dxfId="3" type="firstRowStripe"/>
-      <tableStyleElement dxfId="4" type="secondRowStripe"/>
+      <tableStyleElement dxfId="2" type="firstRowStripe"/>
+      <tableStyleElement dxfId="5" type="secondRowStripe"/>
     </tableStyle>
     <tableStyle count="3" pivot="0" name="平均數據-style">
       <tableStyleElement dxfId="1" type="headerRow"/>
-      <tableStyleElement dxfId="3" type="firstRowStripe"/>
-      <tableStyleElement dxfId="4" type="secondRowStripe"/>
+      <tableStyleElement dxfId="2" type="firstRowStripe"/>
+      <tableStyleElement dxfId="5" type="secondRowStripe"/>
     </tableStyle>
-    <tableStyle count="3" pivot="0" name="2026.10.10 G02 vs 福爾摩沙夢想家-style">
-      <tableStyleElement dxfId="2" type="headerRow"/>
-      <tableStyleElement dxfId="5" type="firstRowStripe"/>
-      <tableStyleElement dxfId="4" type="secondRowStripe"/>
+    <tableStyle count="3" pivot="0" name="2026.10.09 G01 海神 vs 特攻-style">
+      <tableStyleElement dxfId="3" type="headerRow"/>
+      <tableStyleElement dxfId="4" type="firstRowStripe"/>
+      <tableStyleElement dxfId="5" type="secondRowStripe"/>
     </tableStyle>
-    <tableStyle count="3" pivot="0" name="2026.10.09 G01 vs 高雄全家海神-style">
-      <tableStyleElement dxfId="2" type="headerRow"/>
-      <tableStyleElement dxfId="5" type="firstRowStripe"/>
-      <tableStyleElement dxfId="4" type="secondRowStripe"/>
+    <tableStyle count="3" pivot="0" name="2026.10.10 G05 夢想家 vs 特攻-style">
+      <tableStyleElement dxfId="3" type="headerRow"/>
+      <tableStyleElement dxfId="4" type="firstRowStripe"/>
+      <tableStyleElement dxfId="5" type="secondRowStripe"/>
     </tableStyle>
     <tableStyle count="3" pivot="0" name="平均數據-style 2">
       <tableStyleElement dxfId="1" type="headerRow"/>
-      <tableStyleElement dxfId="3" type="firstRowStripe"/>
-      <tableStyleElement dxfId="4" type="secondRowStripe"/>
+      <tableStyleElement dxfId="2" type="firstRowStripe"/>
+      <tableStyleElement dxfId="5" type="secondRowStripe"/>
     </tableStyle>
     <tableStyle count="3" pivot="0" name="平均數據-style 3">
       <tableStyleElement dxfId="1" type="headerRow"/>
-      <tableStyleElement dxfId="3" type="firstRowStripe"/>
-      <tableStyleElement dxfId="4" type="secondRowStripe"/>
+      <tableStyleElement dxfId="2" type="firstRowStripe"/>
+      <tableStyleElement dxfId="5" type="secondRowStripe"/>
     </tableStyle>
     <tableStyle count="3" pivot="0" name="平均數據-style 4">
       <tableStyleElement dxfId="1" type="headerRow"/>
-      <tableStyleElement dxfId="3" type="firstRowStripe"/>
-      <tableStyleElement dxfId="4" type="secondRowStripe"/>
+      <tableStyleElement dxfId="2" type="firstRowStripe"/>
+      <tableStyleElement dxfId="5" type="secondRowStripe"/>
     </tableStyle>
-    <tableStyle count="3" pivot="0" name="2026.10.10 G02 vs 福爾摩沙夢想家-style 2">
-      <tableStyleElement dxfId="2" type="headerRow"/>
-      <tableStyleElement dxfId="5" type="firstRowStripe"/>
-      <tableStyleElement dxfId="4" type="secondRowStripe"/>
+    <tableStyle count="3" pivot="0" name="2026.10.09 G01 海神 vs 特攻-style 2">
+      <tableStyleElement dxfId="3" type="headerRow"/>
+      <tableStyleElement dxfId="4" type="firstRowStripe"/>
+      <tableStyleElement dxfId="5" type="secondRowStripe"/>
     </tableStyle>
-    <tableStyle count="3" pivot="0" name="2026.10.10 G02 vs 福爾摩沙夢想家-style 3">
-      <tableStyleElement dxfId="2" type="headerRow"/>
-      <tableStyleElement dxfId="5" type="firstRowStripe"/>
-      <tableStyleElement dxfId="4" type="secondRowStripe"/>
+    <tableStyle count="3" pivot="0" name="2026.10.10 G05 夢想家 vs 特攻-style 2">
+      <tableStyleElement dxfId="3" type="headerRow"/>
+      <tableStyleElement dxfId="4" type="firstRowStripe"/>
+      <tableStyleElement dxfId="5" type="secondRowStripe"/>
     </tableStyle>
-    <tableStyle count="3" pivot="0" name="2026.10.10 G02 vs 福爾摩沙夢想家-style 4">
-      <tableStyleElement dxfId="2" type="headerRow"/>
-      <tableStyleElement dxfId="5" type="firstRowStripe"/>
-      <tableStyleElement dxfId="4" type="secondRowStripe"/>
+    <tableStyle count="3" pivot="0" name="2026.10.09 G01 海神 vs 特攻-style 3">
+      <tableStyleElement dxfId="3" type="headerRow"/>
+      <tableStyleElement dxfId="4" type="firstRowStripe"/>
+      <tableStyleElement dxfId="5" type="secondRowStripe"/>
     </tableStyle>
-    <tableStyle count="3" pivot="0" name="2026.10.09 G01 vs 高雄全家海神-style 2">
-      <tableStyleElement dxfId="2" type="headerRow"/>
-      <tableStyleElement dxfId="5" type="firstRowStripe"/>
-      <tableStyleElement dxfId="4" type="secondRowStripe"/>
+    <tableStyle count="3" pivot="0" name="2026.10.10 G05 夢想家 vs 特攻-style 3">
+      <tableStyleElement dxfId="3" type="headerRow"/>
+      <tableStyleElement dxfId="4" type="firstRowStripe"/>
+      <tableStyleElement dxfId="5" type="secondRowStripe"/>
     </tableStyle>
-    <tableStyle count="3" pivot="0" name="2026.10.09 G01 vs 高雄全家海神-style 3">
-      <tableStyleElement dxfId="2" type="headerRow"/>
-      <tableStyleElement dxfId="5" type="firstRowStripe"/>
-      <tableStyleElement dxfId="4" type="secondRowStripe"/>
+    <tableStyle count="3" pivot="0" name="2026.10.09 G01 海神 vs 特攻-style 4">
+      <tableStyleElement dxfId="3" type="headerRow"/>
+      <tableStyleElement dxfId="4" type="firstRowStripe"/>
+      <tableStyleElement dxfId="5" type="secondRowStripe"/>
     </tableStyle>
-    <tableStyle count="3" pivot="0" name="2026.10.09 G01 vs 高雄全家海神-style 4">
-      <tableStyleElement dxfId="2" type="headerRow"/>
-      <tableStyleElement dxfId="5" type="firstRowStripe"/>
-      <tableStyleElement dxfId="4" type="secondRowStripe"/>
+    <tableStyle count="3" pivot="0" name="2026.10.10 G05 夢想家 vs 特攻-style 4">
+      <tableStyleElement dxfId="3" type="headerRow"/>
+      <tableStyleElement dxfId="4" type="firstRowStripe"/>
+      <tableStyleElement dxfId="5" type="secondRowStripe"/>
     </tableStyle>
   </tableStyles>
 </styleSheet>
@@ -1004,7 +1004,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" headerRowCount="0" ref="A4:AI19" displayName="Table_3" name="Table_3" id="2">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" headerRowCount="0" ref="A4:AI19" displayName="Table_2" name="Table_2" id="2">
   <tableColumns count="35">
     <tableColumn name="Column1" id="1"/>
     <tableColumn name="Column2" id="2"/>
@@ -1052,7 +1052,7 @@
 </file>
 
 <file path=xl/tables/table10.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A4:AI19" displayName="Table_2" name="Table_2" id="1">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A4:AI19" displayName="Table_1" name="Table_1" id="4">
   <tableColumns count="35">
     <tableColumn name="背號" id="1"/>
     <tableColumn name="球員名" id="2"/>
@@ -1090,12 +1090,12 @@
     <tableColumn name="投籃熱區與進攻特徵分佈" id="34"/>
     <tableColumn name="備註 / 單場表現重點" id="35"/>
   </tableColumns>
-  <tableStyleInfo name="2026.10.10 G02 vs 福爾摩沙夢想家-style" showColumnStripes="0" showFirstColumn="1" showLastColumn="1" showRowStripes="1"/>
+  <tableStyleInfo name="2026.10.10 G05 夢想家 vs 特攻-style" showColumnStripes="0" showFirstColumn="1" showLastColumn="1" showRowStripes="1"/>
 </table>
 </file>
 
 <file path=xl/tables/table11.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="AK4:AQ12" displayName="Table_8" name="Table_8" id="8">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="AK4:AQ12" displayName="Table_9" name="Table_9" id="9">
   <tableColumns count="7">
     <tableColumn name="球員名" id="1"/>
     <tableColumn name="時間" id="2"/>
@@ -1105,12 +1105,12 @@
     <tableColumn name="Off_NetRtg" id="6"/>
     <tableColumn name="Diff" id="7"/>
   </tableColumns>
-  <tableStyleInfo name="2026.10.10 G02 vs 福爾摩沙夢想家-style 2" showColumnStripes="0" showFirstColumn="1" showLastColumn="1" showRowStripes="1"/>
+  <tableStyleInfo name="2026.10.10 G05 夢想家 vs 特攻-style 2" showColumnStripes="0" showFirstColumn="1" showLastColumn="1" showRowStripes="1"/>
 </table>
 </file>
 
 <file path=xl/tables/table12.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="AS4:AX7" displayName="Table_9" name="Table_9" id="9">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="AS4:AX7" displayName="Table_11" name="Table_11" id="10">
   <tableColumns count="6">
     <tableColumn name="五人陣容組合" id="1"/>
     <tableColumn name="時間" id="2"/>
@@ -1119,17 +1119,17 @@
     <tableColumn name="Lineup DRtg" id="5"/>
     <tableColumn name="Lineup NetRtg" id="6"/>
   </tableColumns>
-  <tableStyleInfo name="2026.10.10 G02 vs 福爾摩沙夢想家-style 3" showColumnStripes="0" showFirstColumn="1" showLastColumn="1" showRowStripes="1"/>
+  <tableStyleInfo name="2026.10.10 G05 夢想家 vs 特攻-style 3" showColumnStripes="0" showFirstColumn="1" showLastColumn="1" showRowStripes="1"/>
 </table>
 </file>
 
 <file path=xl/tables/table13.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="AZ4:BA7" displayName="Table_10" name="Table_10" id="10">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="AZ4:BA7" displayName="Table_13" name="Table_13" id="13">
   <tableColumns count="2">
     <tableColumn name="對位情境" id="1"/>
     <tableColumn name="表現與影響" id="2"/>
   </tableColumns>
-  <tableStyleInfo name="2026.10.10 G02 vs 福爾摩沙夢想家-style 4" showColumnStripes="0" showFirstColumn="1" showLastColumn="1" showRowStripes="1"/>
+  <tableStyleInfo name="2026.10.10 G05 夢想家 vs 特攻-style 4" showColumnStripes="0" showFirstColumn="1" showLastColumn="1" showRowStripes="1"/>
 </table>
 </file>
 
@@ -1178,7 +1178,7 @@
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A3:Z17" displayName="Table_1" name="Table_1" id="3">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A3:Z17" displayName="Table_3" name="Table_3" id="1">
   <tableColumns count="26">
     <tableColumn name="球隊" id="1"/>
     <tableColumn name="背號" id="2"/>
@@ -1212,7 +1212,7 @@
 </file>
 
 <file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A4:AI19" displayName="Table_4" name="Table_4" id="4">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A4:AI19" displayName="Table_4" name="Table_4" id="3">
   <tableColumns count="35">
     <tableColumn name="背號" id="1"/>
     <tableColumn name="球員名" id="2"/>
@@ -1250,12 +1250,12 @@
     <tableColumn name="投籃熱區與進攻特徵分佈" id="34"/>
     <tableColumn name="備註 / 單場表現重點" id="35"/>
   </tableColumns>
-  <tableStyleInfo name="2026.10.09 G01 vs 高雄全家海神-style" showColumnStripes="0" showFirstColumn="1" showLastColumn="1" showRowStripes="1"/>
+  <tableStyleInfo name="2026.10.09 G01 海神 vs 特攻-style" showColumnStripes="0" showFirstColumn="1" showLastColumn="1" showRowStripes="1"/>
 </table>
 </file>
 
 <file path=xl/tables/table7.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="AK4:AQ12" displayName="Table_11" name="Table_11" id="11">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="AK4:AQ12" displayName="Table_8" name="Table_8" id="8">
   <tableColumns count="7">
     <tableColumn name="球員名" id="1"/>
     <tableColumn name="時間" id="2"/>
@@ -1265,12 +1265,12 @@
     <tableColumn name="Off_NetRtg" id="6"/>
     <tableColumn name="Diff" id="7"/>
   </tableColumns>
-  <tableStyleInfo name="2026.10.09 G01 vs 高雄全家海神-style 2" showColumnStripes="0" showFirstColumn="1" showLastColumn="1" showRowStripes="1"/>
+  <tableStyleInfo name="2026.10.09 G01 海神 vs 特攻-style 2" showColumnStripes="0" showFirstColumn="1" showLastColumn="1" showRowStripes="1"/>
 </table>
 </file>
 
 <file path=xl/tables/table8.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="AS4:AX7" displayName="Table_12" name="Table_12" id="12">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="AS4:AX7" displayName="Table_10" name="Table_10" id="11">
   <tableColumns count="6">
     <tableColumn name="五人陣容組合" id="1"/>
     <tableColumn name="時間" id="2"/>
@@ -1279,17 +1279,17 @@
     <tableColumn name="Lineup DRtg" id="5"/>
     <tableColumn name="Lineup NetRtg" id="6"/>
   </tableColumns>
-  <tableStyleInfo name="2026.10.09 G01 vs 高雄全家海神-style 3" showColumnStripes="0" showFirstColumn="1" showLastColumn="1" showRowStripes="1"/>
+  <tableStyleInfo name="2026.10.09 G01 海神 vs 特攻-style 3" showColumnStripes="0" showFirstColumn="1" showLastColumn="1" showRowStripes="1"/>
 </table>
 </file>
 
 <file path=xl/tables/table9.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="AZ4:BA7" displayName="Table_13" name="Table_13" id="13">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="AZ4:BA7" displayName="Table_12" name="Table_12" id="12">
   <tableColumns count="2">
     <tableColumn name="對位情境" id="1"/>
     <tableColumn name="表現與影響" id="2"/>
   </tableColumns>
-  <tableStyleInfo name="2026.10.09 G01 vs 高雄全家海神-style 4" showColumnStripes="0" showFirstColumn="1" showLastColumn="1" showRowStripes="1"/>
+  <tableStyleInfo name="2026.10.09 G01 海神 vs 特攻-style 4" showColumnStripes="0" showFirstColumn="1" showLastColumn="1" showRowStripes="1"/>
 </table>
 </file>
 
@@ -1541,182 +1541,182 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>15</v>
+        <v>1</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="s">
-        <v>25</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="s">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>33</v>
+        <v>9</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E4" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="G4" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="H4" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I4" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="J4" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="K4" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="L4" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="M4" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="N4" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="O4" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="P4" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="Q4" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="R4" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="S4" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="T4" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="U4" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="F4" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="G4" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="H4" s="2" t="s">
+      <c r="V4" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="I4" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="J4" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="K4" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="L4" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="M4" s="2" t="s">
+      <c r="W4" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="N4" s="2" t="s">
+      <c r="X4" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="O4" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="P4" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="Q4" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="R4" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="S4" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="T4" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="U4" s="2" t="s">
+      <c r="Y4" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="Z4" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="AA4" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="V4" s="2" t="s">
+      <c r="AB4" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="W4" s="2" t="s">
+      <c r="AC4" s="2" t="s">
         <v>45</v>
-      </c>
-      <c r="X4" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="Y4" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="Z4" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="AA4" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="AB4" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="AC4" s="2" t="s">
-        <v>53</v>
       </c>
       <c r="AD4" s="5" t="str">
         <v>#ERROR!</v>
       </c>
       <c r="AE4" s="2" t="s">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="AF4" s="2" t="s">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="AG4" s="2" t="s">
-        <v>28</v>
+        <v>37</v>
       </c>
       <c r="AH4" s="2" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="AI4" s="2" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="AJ4" s="6"/>
       <c r="AK4" s="2" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AL4" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="AM4" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="AN4" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="AO4" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="AP4" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="AM4" s="2" t="s">
+      <c r="AQ4" s="2" t="s">
         <v>61</v>
-      </c>
-      <c r="AN4" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="AO4" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="AP4" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="AQ4" s="2" t="s">
-        <v>65</v>
       </c>
       <c r="AR4" s="6"/>
       <c r="AS4" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="AT4" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="AU4" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="AV4" s="2" t="s">
         <v>66</v>
       </c>
-      <c r="AT4" s="2" t="s">
+      <c r="AW4" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="AU4" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="AV4" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="AW4" s="2" t="s">
-        <v>72</v>
-      </c>
       <c r="AX4" s="2" t="s">
-        <v>73</v>
+        <v>68</v>
       </c>
       <c r="AY4" s="6"/>
       <c r="AZ4" s="2" t="s">
-        <v>74</v>
+        <v>69</v>
       </c>
       <c r="BA4" s="2" t="s">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="BB4" s="2" t="s">
-        <v>76</v>
+        <v>71</v>
       </c>
       <c r="BC4" s="2" t="s">
-        <v>71</v>
+        <v>66</v>
       </c>
       <c r="BD4" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="BE4" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="BF4" s="2" t="s">
         <v>72</v>
-      </c>
-      <c r="BE4" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="BF4" s="2" t="s">
-        <v>77</v>
       </c>
     </row>
     <row r="5">
@@ -1724,16 +1724,16 @@
         <v>61.0</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>31</v>
+        <v>47</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>32</v>
+        <v>48</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="F5" s="3">
         <v>2.0</v>
@@ -1807,7 +1807,7 @@
       <c r="AC5" s="3">
         <v>28.5</v>
       </c>
-      <c r="AD5" s="8">
+      <c r="AD5" s="9">
         <v>5.5</v>
       </c>
       <c r="AE5" s="4">
@@ -1820,14 +1820,14 @@
         <v>2.5</v>
       </c>
       <c r="AH5" s="3" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="AI5" s="3" t="s">
-        <v>89</v>
-      </c>
-      <c r="AJ5" s="9"/>
+        <v>85</v>
+      </c>
+      <c r="AJ5" s="10"/>
       <c r="AK5" s="3" t="s">
-        <v>92</v>
+        <v>87</v>
       </c>
       <c r="AL5" s="7">
         <v>2.459722222222222</v>
@@ -1838,23 +1838,23 @@
       <c r="AN5" s="3">
         <v>105.2</v>
       </c>
-      <c r="AO5" s="8">
+      <c r="AO5" s="9">
         <v>10.6</v>
       </c>
       <c r="AP5" s="3">
         <v>-13.4</v>
       </c>
-      <c r="AQ5" s="8">
+      <c r="AQ5" s="9">
         <v>24</v>
       </c>
-      <c r="AR5" s="9"/>
+      <c r="AR5" s="10"/>
       <c r="AS5" s="3" t="s">
-        <v>93</v>
-      </c>
-      <c r="AT5" s="13">
+        <v>89</v>
+      </c>
+      <c r="AT5" s="12">
         <v>0.7638888888888888</v>
       </c>
-      <c r="AU5" s="8">
+      <c r="AU5" s="9">
         <v>15</v>
       </c>
       <c r="AV5" s="3">
@@ -1863,17 +1863,17 @@
       <c r="AW5" s="3">
         <v>99.5</v>
       </c>
-      <c r="AX5" s="8">
+      <c r="AX5" s="9">
         <v>23</v>
       </c>
-      <c r="AY5" s="9"/>
+      <c r="AY5" s="10"/>
       <c r="AZ5" s="3" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="BA5" s="7">
         <v>1.6111111111111112</v>
       </c>
-      <c r="BB5" s="8">
+      <c r="BB5" s="9">
         <v>14</v>
       </c>
       <c r="BC5" s="3">
@@ -1882,11 +1882,11 @@
       <c r="BD5" s="3">
         <v>103.8</v>
       </c>
-      <c r="BE5" s="8">
+      <c r="BE5" s="9">
         <v>14.7</v>
       </c>
       <c r="BF5" s="3" t="s">
-        <v>97</v>
+        <v>105</v>
       </c>
     </row>
     <row r="6">
@@ -1894,16 +1894,16 @@
         <v>10.0</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>40</v>
+        <v>49</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>41</v>
+        <v>50</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>42</v>
+        <v>51</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>99</v>
+        <v>107</v>
       </c>
       <c r="F6" s="3">
         <v>2.0</v>
@@ -1977,7 +1977,7 @@
       <c r="AC6" s="3">
         <v>15.5</v>
       </c>
-      <c r="AD6" s="8">
+      <c r="AD6" s="9">
         <v>2.5</v>
       </c>
       <c r="AE6" s="4">
@@ -1990,14 +1990,14 @@
         <v>1.33</v>
       </c>
       <c r="AH6" s="3" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="AI6" s="3" t="s">
-        <v>109</v>
-      </c>
-      <c r="AJ6" s="9"/>
+        <v>111</v>
+      </c>
+      <c r="AJ6" s="10"/>
       <c r="AK6" s="3" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="AL6" s="7">
         <v>2.1875</v>
@@ -2008,23 +2008,23 @@
       <c r="AN6" s="3">
         <v>106.8</v>
       </c>
-      <c r="AO6" s="8">
+      <c r="AO6" s="9">
         <v>7.4</v>
       </c>
       <c r="AP6" s="3">
         <v>-10.5</v>
       </c>
-      <c r="AQ6" s="8">
+      <c r="AQ6" s="9">
         <v>17.9</v>
       </c>
-      <c r="AR6" s="9"/>
+      <c r="AR6" s="10"/>
       <c r="AS6" s="3" t="s">
-        <v>111</v>
-      </c>
-      <c r="AT6" s="13">
+        <v>119</v>
+      </c>
+      <c r="AT6" s="12">
         <v>0.5486111111111112</v>
       </c>
-      <c r="AU6" s="8">
+      <c r="AU6" s="9">
         <v>7</v>
       </c>
       <c r="AV6" s="3">
@@ -2033,17 +2033,17 @@
       <c r="AW6" s="3">
         <v>104.2</v>
       </c>
-      <c r="AX6" s="8">
+      <c r="AX6" s="9">
         <v>12.6</v>
       </c>
-      <c r="AY6" s="9"/>
+      <c r="AY6" s="10"/>
       <c r="AZ6" s="3" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="BA6" s="7">
         <v>1.0104166666666667</v>
       </c>
-      <c r="BB6" s="8">
+      <c r="BB6" s="9">
         <v>2</v>
       </c>
       <c r="BC6" s="3">
@@ -2052,11 +2052,11 @@
       <c r="BD6" s="3">
         <v>109.5</v>
       </c>
-      <c r="BE6" s="8">
+      <c r="BE6" s="9">
         <v>2.5</v>
       </c>
       <c r="BF6" s="3" t="s">
-        <v>116</v>
+        <v>122</v>
       </c>
     </row>
     <row r="7">
@@ -2064,21 +2064,21 @@
         <v>28.0</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>31</v>
+        <v>47</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="F7" s="3">
         <v>2.0</v>
       </c>
-      <c r="G7" s="13">
+      <c r="G7" s="12">
         <v>0.8645833333333334</v>
       </c>
       <c r="H7" s="3">
@@ -2160,14 +2160,14 @@
         <v>0.33</v>
       </c>
       <c r="AH7" s="3" t="s">
-        <v>117</v>
+        <v>129</v>
       </c>
       <c r="AI7" s="3" t="s">
-        <v>118</v>
-      </c>
-      <c r="AJ7" s="9"/>
+        <v>131</v>
+      </c>
+      <c r="AJ7" s="10"/>
       <c r="AK7" s="3" t="s">
-        <v>119</v>
+        <v>132</v>
       </c>
       <c r="AL7" s="7">
         <v>1.9444444444444444</v>
@@ -2178,20 +2178,20 @@
       <c r="AN7" s="3">
         <v>108.0</v>
       </c>
-      <c r="AO7" s="8">
+      <c r="AO7" s="9">
         <v>4.5</v>
       </c>
       <c r="AP7" s="3">
         <v>-6.2</v>
       </c>
-      <c r="AQ7" s="8">
+      <c r="AQ7" s="9">
         <v>10.7</v>
       </c>
-      <c r="AR7" s="9"/>
+      <c r="AR7" s="10"/>
       <c r="AS7" s="3" t="s">
-        <v>121</v>
-      </c>
-      <c r="AT7" s="13">
+        <v>134</v>
+      </c>
+      <c r="AT7" s="12">
         <v>0.4895833333333333</v>
       </c>
       <c r="AU7" s="3">
@@ -2206,11 +2206,11 @@
       <c r="AX7" s="3">
         <v>-7.8</v>
       </c>
-      <c r="AY7" s="9"/>
+      <c r="AY7" s="10"/>
       <c r="AZ7" s="3" t="s">
-        <v>122</v>
-      </c>
-      <c r="BA7" s="13">
+        <v>136</v>
+      </c>
+      <c r="BA7" s="12">
         <v>0.7708333333333334</v>
       </c>
       <c r="BB7" s="3">
@@ -2226,7 +2226,7 @@
         <v>-10.5</v>
       </c>
       <c r="BF7" s="3" t="s">
-        <v>123</v>
+        <v>141</v>
       </c>
     </row>
     <row r="8">
@@ -2234,16 +2234,16 @@
         <v>17.0</v>
       </c>
       <c r="B8" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="D8" s="3" t="s">
         <v>54</v>
       </c>
-      <c r="C8" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="D8" s="3" t="s">
-        <v>50</v>
-      </c>
       <c r="E8" s="3" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="F8" s="3">
         <v>2.0</v>
@@ -2330,14 +2330,14 @@
         <v>2.0</v>
       </c>
       <c r="AH8" s="3" t="s">
-        <v>127</v>
+        <v>146</v>
       </c>
       <c r="AI8" s="3" t="s">
-        <v>128</v>
-      </c>
-      <c r="AJ8" s="9"/>
+        <v>147</v>
+      </c>
+      <c r="AJ8" s="10"/>
       <c r="AK8" s="3" t="s">
-        <v>129</v>
+        <v>148</v>
       </c>
       <c r="AL8" s="7">
         <v>1.4722222222222223</v>
@@ -2348,51 +2348,51 @@
       <c r="AN8" s="3">
         <v>107.5</v>
       </c>
-      <c r="AO8" s="8">
+      <c r="AO8" s="9">
         <v>3.3</v>
       </c>
       <c r="AP8" s="3">
         <v>-4.0</v>
       </c>
-      <c r="AQ8" s="8">
+      <c r="AQ8" s="9">
         <v>7.3</v>
       </c>
-      <c r="AR8" s="9"/>
-      <c r="AS8" s="9"/>
-      <c r="AT8" s="9"/>
-      <c r="AU8" s="9"/>
-      <c r="AV8" s="9"/>
-      <c r="AW8" s="9"/>
-      <c r="AX8" s="9"/>
-      <c r="AY8" s="9"/>
-      <c r="AZ8" s="9"/>
-      <c r="BA8" s="9"/>
-      <c r="BB8" s="9"/>
-      <c r="BC8" s="9"/>
-      <c r="BD8" s="9"/>
-      <c r="BE8" s="9"/>
-      <c r="BF8" s="9"/>
+      <c r="AR8" s="10"/>
+      <c r="AS8" s="10"/>
+      <c r="AT8" s="10"/>
+      <c r="AU8" s="10"/>
+      <c r="AV8" s="10"/>
+      <c r="AW8" s="10"/>
+      <c r="AX8" s="10"/>
+      <c r="AY8" s="10"/>
+      <c r="AZ8" s="10"/>
+      <c r="BA8" s="10"/>
+      <c r="BB8" s="10"/>
+      <c r="BC8" s="10"/>
+      <c r="BD8" s="10"/>
+      <c r="BE8" s="10"/>
+      <c r="BF8" s="10"/>
     </row>
     <row r="9">
       <c r="A9" s="3">
         <v>20.0</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>55</v>
+        <v>73</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>41</v>
+        <v>50</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>56</v>
+        <v>74</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>99</v>
+        <v>107</v>
       </c>
       <c r="F9" s="3">
         <v>2.0</v>
       </c>
-      <c r="G9" s="13">
+      <c r="G9" s="12">
         <v>0.9722222222222222</v>
       </c>
       <c r="H9" s="3">
@@ -2461,7 +2461,7 @@
       <c r="AC9" s="3">
         <v>11.0</v>
       </c>
-      <c r="AD9" s="8">
+      <c r="AD9" s="9">
         <v>8.5</v>
       </c>
       <c r="AE9" s="4">
@@ -2474,14 +2474,14 @@
         <v>1.8</v>
       </c>
       <c r="AH9" s="3" t="s">
-        <v>137</v>
+        <v>157</v>
       </c>
       <c r="AI9" s="3" t="s">
-        <v>138</v>
-      </c>
-      <c r="AJ9" s="9"/>
+        <v>158</v>
+      </c>
+      <c r="AJ9" s="10"/>
       <c r="AK9" s="3" t="s">
-        <v>139</v>
+        <v>159</v>
       </c>
       <c r="AL9" s="7">
         <v>1.1805555555555556</v>
@@ -2492,51 +2492,51 @@
       <c r="AN9" s="3">
         <v>108.4</v>
       </c>
-      <c r="AO9" s="8">
+      <c r="AO9" s="9">
         <v>1.1</v>
       </c>
       <c r="AP9" s="3">
         <v>-2.5</v>
       </c>
-      <c r="AQ9" s="8">
+      <c r="AQ9" s="9">
         <v>3.6</v>
       </c>
-      <c r="AR9" s="9"/>
-      <c r="AS9" s="9"/>
-      <c r="AT9" s="9"/>
-      <c r="AU9" s="9"/>
-      <c r="AV9" s="9"/>
-      <c r="AW9" s="9"/>
-      <c r="AX9" s="9"/>
-      <c r="AY9" s="9"/>
-      <c r="AZ9" s="9"/>
-      <c r="BA9" s="9"/>
-      <c r="BB9" s="9"/>
-      <c r="BC9" s="9"/>
-      <c r="BD9" s="9"/>
-      <c r="BE9" s="9"/>
-      <c r="BF9" s="9"/>
+      <c r="AR9" s="10"/>
+      <c r="AS9" s="10"/>
+      <c r="AT9" s="10"/>
+      <c r="AU9" s="10"/>
+      <c r="AV9" s="10"/>
+      <c r="AW9" s="10"/>
+      <c r="AX9" s="10"/>
+      <c r="AY9" s="10"/>
+      <c r="AZ9" s="10"/>
+      <c r="BA9" s="10"/>
+      <c r="BB9" s="10"/>
+      <c r="BC9" s="10"/>
+      <c r="BD9" s="10"/>
+      <c r="BE9" s="10"/>
+      <c r="BF9" s="10"/>
     </row>
     <row r="10">
       <c r="A10" s="3">
         <v>0.0</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>59</v>
+        <v>76</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>41</v>
+        <v>50</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>42</v>
+        <v>51</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>99</v>
+        <v>107</v>
       </c>
       <c r="F10" s="3">
         <v>2.0</v>
       </c>
-      <c r="G10" s="13">
+      <c r="G10" s="12">
         <v>0.9270833333333334</v>
       </c>
       <c r="H10" s="3">
@@ -2605,7 +2605,7 @@
       <c r="AC10" s="3">
         <v>7.5</v>
       </c>
-      <c r="AD10" s="8">
+      <c r="AD10" s="9">
         <v>9.5</v>
       </c>
       <c r="AE10" s="4">
@@ -2618,14 +2618,14 @@
         <v>1.0</v>
       </c>
       <c r="AH10" s="3" t="s">
-        <v>149</v>
+        <v>167</v>
       </c>
       <c r="AI10" s="3" t="s">
-        <v>151</v>
-      </c>
-      <c r="AJ10" s="9"/>
+        <v>168</v>
+      </c>
+      <c r="AJ10" s="10"/>
       <c r="AK10" s="3" t="s">
-        <v>152</v>
+        <v>116</v>
       </c>
       <c r="AL10" s="7">
         <v>2.263888888888889</v>
@@ -2645,42 +2645,42 @@
       <c r="AQ10" s="3">
         <v>-0.8</v>
       </c>
-      <c r="AR10" s="9"/>
-      <c r="AS10" s="9"/>
-      <c r="AT10" s="9"/>
-      <c r="AU10" s="9"/>
-      <c r="AV10" s="9"/>
-      <c r="AW10" s="9"/>
-      <c r="AX10" s="9"/>
-      <c r="AY10" s="9"/>
-      <c r="AZ10" s="9"/>
-      <c r="BA10" s="9"/>
-      <c r="BB10" s="9"/>
-      <c r="BC10" s="9"/>
-      <c r="BD10" s="9"/>
-      <c r="BE10" s="9"/>
-      <c r="BF10" s="9"/>
+      <c r="AR10" s="10"/>
+      <c r="AS10" s="10"/>
+      <c r="AT10" s="10"/>
+      <c r="AU10" s="10"/>
+      <c r="AV10" s="10"/>
+      <c r="AW10" s="10"/>
+      <c r="AX10" s="10"/>
+      <c r="AY10" s="10"/>
+      <c r="AZ10" s="10"/>
+      <c r="BA10" s="10"/>
+      <c r="BB10" s="10"/>
+      <c r="BC10" s="10"/>
+      <c r="BD10" s="10"/>
+      <c r="BE10" s="10"/>
+      <c r="BF10" s="10"/>
     </row>
     <row r="11">
       <c r="A11" s="3">
         <v>24.0</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>68</v>
+        <v>78</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>41</v>
+        <v>50</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>70</v>
+        <v>79</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>155</v>
+        <v>170</v>
       </c>
       <c r="F11" s="3">
         <v>2.0</v>
       </c>
-      <c r="G11" s="13">
+      <c r="G11" s="12">
         <v>0.7361111111111112</v>
       </c>
       <c r="H11" s="3">
@@ -2749,7 +2749,7 @@
       <c r="AC11" s="3">
         <v>10.0</v>
       </c>
-      <c r="AD11" s="8">
+      <c r="AD11" s="9">
         <v>2</v>
       </c>
       <c r="AE11" s="4">
@@ -2762,14 +2762,14 @@
         <v>2.0</v>
       </c>
       <c r="AH11" s="3" t="s">
-        <v>117</v>
+        <v>129</v>
       </c>
       <c r="AI11" s="3" t="s">
-        <v>160</v>
-      </c>
-      <c r="AJ11" s="9"/>
+        <v>174</v>
+      </c>
+      <c r="AJ11" s="10"/>
       <c r="AK11" s="3" t="s">
-        <v>162</v>
+        <v>175</v>
       </c>
       <c r="AL11" s="7">
         <v>1.125</v>
@@ -2783,48 +2783,48 @@
       <c r="AO11" s="3">
         <v>-4.5</v>
       </c>
-      <c r="AP11" s="8">
+      <c r="AP11" s="9">
         <v>2</v>
       </c>
       <c r="AQ11" s="3">
         <v>-6.5</v>
       </c>
-      <c r="AR11" s="9"/>
-      <c r="AS11" s="9"/>
-      <c r="AT11" s="9"/>
-      <c r="AU11" s="9"/>
-      <c r="AV11" s="9"/>
-      <c r="AW11" s="9"/>
-      <c r="AX11" s="9"/>
-      <c r="AY11" s="9"/>
-      <c r="AZ11" s="9"/>
-      <c r="BA11" s="9"/>
-      <c r="BB11" s="9"/>
-      <c r="BC11" s="9"/>
-      <c r="BD11" s="9"/>
-      <c r="BE11" s="9"/>
-      <c r="BF11" s="9"/>
+      <c r="AR11" s="10"/>
+      <c r="AS11" s="10"/>
+      <c r="AT11" s="10"/>
+      <c r="AU11" s="10"/>
+      <c r="AV11" s="10"/>
+      <c r="AW11" s="10"/>
+      <c r="AX11" s="10"/>
+      <c r="AY11" s="10"/>
+      <c r="AZ11" s="10"/>
+      <c r="BA11" s="10"/>
+      <c r="BB11" s="10"/>
+      <c r="BC11" s="10"/>
+      <c r="BD11" s="10"/>
+      <c r="BE11" s="10"/>
+      <c r="BF11" s="10"/>
     </row>
     <row r="12">
       <c r="A12" s="3">
         <v>7.0</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>41</v>
+        <v>50</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>56</v>
+        <v>74</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>165</v>
+        <v>182</v>
       </c>
       <c r="F12" s="3">
         <v>2.0</v>
       </c>
-      <c r="G12" s="13">
+      <c r="G12" s="12">
         <v>0.5902777777777778</v>
       </c>
       <c r="H12" s="3">
@@ -2893,7 +2893,7 @@
       <c r="AC12" s="3">
         <v>5.0</v>
       </c>
-      <c r="AD12" s="8">
+      <c r="AD12" s="9">
         <v>4.5</v>
       </c>
       <c r="AE12" s="4">
@@ -2906,14 +2906,14 @@
         <v>1.67</v>
       </c>
       <c r="AH12" s="3" t="s">
-        <v>169</v>
+        <v>187</v>
       </c>
       <c r="AI12" s="3" t="s">
-        <v>170</v>
-      </c>
-      <c r="AJ12" s="9"/>
+        <v>188</v>
+      </c>
+      <c r="AJ12" s="10"/>
       <c r="AK12" s="3" t="s">
-        <v>148</v>
+        <v>165</v>
       </c>
       <c r="AL12" s="7">
         <v>1.7291666666666667</v>
@@ -2927,48 +2927,48 @@
       <c r="AO12" s="3">
         <v>-7.8</v>
       </c>
-      <c r="AP12" s="8">
+      <c r="AP12" s="9">
         <v>5.2</v>
       </c>
       <c r="AQ12" s="3">
         <v>-13.0</v>
       </c>
-      <c r="AR12" s="9"/>
-      <c r="AS12" s="9"/>
-      <c r="AT12" s="9"/>
-      <c r="AU12" s="9"/>
-      <c r="AV12" s="9"/>
-      <c r="AW12" s="9"/>
-      <c r="AX12" s="9"/>
-      <c r="AY12" s="9"/>
-      <c r="AZ12" s="9"/>
-      <c r="BA12" s="9"/>
-      <c r="BB12" s="9"/>
-      <c r="BC12" s="9"/>
-      <c r="BD12" s="9"/>
-      <c r="BE12" s="9"/>
-      <c r="BF12" s="9"/>
+      <c r="AR12" s="10"/>
+      <c r="AS12" s="10"/>
+      <c r="AT12" s="10"/>
+      <c r="AU12" s="10"/>
+      <c r="AV12" s="10"/>
+      <c r="AW12" s="10"/>
+      <c r="AX12" s="10"/>
+      <c r="AY12" s="10"/>
+      <c r="AZ12" s="10"/>
+      <c r="BA12" s="10"/>
+      <c r="BB12" s="10"/>
+      <c r="BC12" s="10"/>
+      <c r="BD12" s="10"/>
+      <c r="BE12" s="10"/>
+      <c r="BF12" s="10"/>
     </row>
     <row r="13">
       <c r="A13" s="3">
         <v>77.0</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>80</v>
+        <v>86</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>41</v>
+        <v>50</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>173</v>
+        <v>196</v>
       </c>
       <c r="F13" s="3">
         <v>2.0</v>
       </c>
-      <c r="G13" s="13">
+      <c r="G13" s="12">
         <v>0.5625</v>
       </c>
       <c r="H13" s="3">
@@ -3050,55 +3050,55 @@
         <v>5.0</v>
       </c>
       <c r="AH13" s="3" t="s">
-        <v>177</v>
+        <v>200</v>
       </c>
       <c r="AI13" s="3" t="s">
-        <v>178</v>
-      </c>
-      <c r="AJ13" s="9"/>
-      <c r="AK13" s="9"/>
-      <c r="AL13" s="9"/>
-      <c r="AM13" s="9"/>
-      <c r="AN13" s="9"/>
-      <c r="AO13" s="9"/>
-      <c r="AP13" s="9"/>
-      <c r="AQ13" s="9"/>
-      <c r="AR13" s="9"/>
-      <c r="AS13" s="9"/>
-      <c r="AT13" s="9"/>
-      <c r="AU13" s="9"/>
-      <c r="AV13" s="9"/>
-      <c r="AW13" s="9"/>
-      <c r="AX13" s="9"/>
-      <c r="AY13" s="9"/>
-      <c r="AZ13" s="9"/>
-      <c r="BA13" s="9"/>
-      <c r="BB13" s="9"/>
-      <c r="BC13" s="9"/>
-      <c r="BD13" s="9"/>
-      <c r="BE13" s="9"/>
-      <c r="BF13" s="9"/>
+        <v>201</v>
+      </c>
+      <c r="AJ13" s="10"/>
+      <c r="AK13" s="10"/>
+      <c r="AL13" s="10"/>
+      <c r="AM13" s="10"/>
+      <c r="AN13" s="10"/>
+      <c r="AO13" s="10"/>
+      <c r="AP13" s="10"/>
+      <c r="AQ13" s="10"/>
+      <c r="AR13" s="10"/>
+      <c r="AS13" s="10"/>
+      <c r="AT13" s="10"/>
+      <c r="AU13" s="10"/>
+      <c r="AV13" s="10"/>
+      <c r="AW13" s="10"/>
+      <c r="AX13" s="10"/>
+      <c r="AY13" s="10"/>
+      <c r="AZ13" s="10"/>
+      <c r="BA13" s="10"/>
+      <c r="BB13" s="10"/>
+      <c r="BC13" s="10"/>
+      <c r="BD13" s="10"/>
+      <c r="BE13" s="10"/>
+      <c r="BF13" s="10"/>
     </row>
     <row r="14">
       <c r="A14" s="3">
         <v>14.0</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>81</v>
+        <v>88</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>41</v>
+        <v>50</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>70</v>
+        <v>79</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>181</v>
+        <v>205</v>
       </c>
       <c r="F14" s="3">
         <v>2.0</v>
       </c>
-      <c r="G14" s="13">
+      <c r="G14" s="12">
         <v>0.4722222222222222</v>
       </c>
       <c r="H14" s="3">
@@ -3167,7 +3167,7 @@
       <c r="AC14" s="3">
         <v>4.5</v>
       </c>
-      <c r="AD14" s="8">
+      <c r="AD14" s="9">
         <v>5.5</v>
       </c>
       <c r="AE14" s="4">
@@ -3180,55 +3180,55 @@
         <v>1.0</v>
       </c>
       <c r="AH14" s="3" t="s">
-        <v>184</v>
+        <v>211</v>
       </c>
       <c r="AI14" s="3" t="s">
-        <v>185</v>
-      </c>
-      <c r="AJ14" s="9"/>
-      <c r="AK14" s="9"/>
-      <c r="AL14" s="9"/>
-      <c r="AM14" s="9"/>
-      <c r="AN14" s="9"/>
-      <c r="AO14" s="9"/>
-      <c r="AP14" s="9"/>
-      <c r="AQ14" s="9"/>
-      <c r="AR14" s="9"/>
-      <c r="AS14" s="9"/>
-      <c r="AT14" s="9"/>
-      <c r="AU14" s="9"/>
-      <c r="AV14" s="9"/>
-      <c r="AW14" s="9"/>
-      <c r="AX14" s="9"/>
-      <c r="AY14" s="9"/>
-      <c r="AZ14" s="9"/>
-      <c r="BA14" s="9"/>
-      <c r="BB14" s="9"/>
-      <c r="BC14" s="9"/>
-      <c r="BD14" s="9"/>
-      <c r="BE14" s="9"/>
-      <c r="BF14" s="9"/>
+        <v>212</v>
+      </c>
+      <c r="AJ14" s="10"/>
+      <c r="AK14" s="10"/>
+      <c r="AL14" s="10"/>
+      <c r="AM14" s="10"/>
+      <c r="AN14" s="10"/>
+      <c r="AO14" s="10"/>
+      <c r="AP14" s="10"/>
+      <c r="AQ14" s="10"/>
+      <c r="AR14" s="10"/>
+      <c r="AS14" s="10"/>
+      <c r="AT14" s="10"/>
+      <c r="AU14" s="10"/>
+      <c r="AV14" s="10"/>
+      <c r="AW14" s="10"/>
+      <c r="AX14" s="10"/>
+      <c r="AY14" s="10"/>
+      <c r="AZ14" s="10"/>
+      <c r="BA14" s="10"/>
+      <c r="BB14" s="10"/>
+      <c r="BC14" s="10"/>
+      <c r="BD14" s="10"/>
+      <c r="BE14" s="10"/>
+      <c r="BF14" s="10"/>
     </row>
     <row r="15">
       <c r="A15" s="3">
         <v>76.0</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>41</v>
+        <v>50</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>161</v>
+        <v>181</v>
       </c>
       <c r="F15" s="3">
         <v>2.0</v>
       </c>
-      <c r="G15" s="13">
+      <c r="G15" s="12">
         <v>0.3645833333333333</v>
       </c>
       <c r="H15" s="3">
@@ -3310,55 +3310,55 @@
         <v>0.0</v>
       </c>
       <c r="AH15" s="3" t="s">
-        <v>190</v>
+        <v>144</v>
       </c>
       <c r="AI15" s="3" t="s">
-        <v>191</v>
-      </c>
-      <c r="AJ15" s="9"/>
-      <c r="AK15" s="9"/>
-      <c r="AL15" s="9"/>
-      <c r="AM15" s="9"/>
-      <c r="AN15" s="9"/>
-      <c r="AO15" s="9"/>
-      <c r="AP15" s="9"/>
-      <c r="AQ15" s="9"/>
-      <c r="AR15" s="9"/>
-      <c r="AS15" s="9"/>
-      <c r="AT15" s="9"/>
-      <c r="AU15" s="9"/>
-      <c r="AV15" s="9"/>
-      <c r="AW15" s="9"/>
-      <c r="AX15" s="9"/>
-      <c r="AY15" s="9"/>
-      <c r="AZ15" s="9"/>
-      <c r="BA15" s="9"/>
-      <c r="BB15" s="9"/>
-      <c r="BC15" s="9"/>
-      <c r="BD15" s="9"/>
-      <c r="BE15" s="9"/>
-      <c r="BF15" s="9"/>
+        <v>220</v>
+      </c>
+      <c r="AJ15" s="10"/>
+      <c r="AK15" s="10"/>
+      <c r="AL15" s="10"/>
+      <c r="AM15" s="10"/>
+      <c r="AN15" s="10"/>
+      <c r="AO15" s="10"/>
+      <c r="AP15" s="10"/>
+      <c r="AQ15" s="10"/>
+      <c r="AR15" s="10"/>
+      <c r="AS15" s="10"/>
+      <c r="AT15" s="10"/>
+      <c r="AU15" s="10"/>
+      <c r="AV15" s="10"/>
+      <c r="AW15" s="10"/>
+      <c r="AX15" s="10"/>
+      <c r="AY15" s="10"/>
+      <c r="AZ15" s="10"/>
+      <c r="BA15" s="10"/>
+      <c r="BB15" s="10"/>
+      <c r="BC15" s="10"/>
+      <c r="BD15" s="10"/>
+      <c r="BE15" s="10"/>
+      <c r="BF15" s="10"/>
     </row>
     <row r="16">
       <c r="A16" s="3">
         <v>12.0</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>84</v>
+        <v>102</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>41</v>
+        <v>50</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>194</v>
+        <v>226</v>
       </c>
       <c r="F16" s="3">
         <v>2.0</v>
       </c>
-      <c r="G16" s="13">
+      <c r="G16" s="12">
         <v>0.2708333333333333</v>
       </c>
       <c r="H16" s="3">
@@ -3440,55 +3440,55 @@
         <v>1.0</v>
       </c>
       <c r="AH16" s="3" t="s">
-        <v>195</v>
+        <v>230</v>
       </c>
       <c r="AI16" s="3" t="s">
-        <v>196</v>
-      </c>
-      <c r="AJ16" s="9"/>
-      <c r="AK16" s="9"/>
-      <c r="AL16" s="9"/>
-      <c r="AM16" s="9"/>
-      <c r="AN16" s="9"/>
-      <c r="AO16" s="9"/>
-      <c r="AP16" s="9"/>
-      <c r="AQ16" s="9"/>
-      <c r="AR16" s="9"/>
-      <c r="AS16" s="9"/>
-      <c r="AT16" s="9"/>
-      <c r="AU16" s="9"/>
-      <c r="AV16" s="9"/>
-      <c r="AW16" s="9"/>
-      <c r="AX16" s="9"/>
-      <c r="AY16" s="9"/>
-      <c r="AZ16" s="9"/>
-      <c r="BA16" s="9"/>
-      <c r="BB16" s="9"/>
-      <c r="BC16" s="9"/>
-      <c r="BD16" s="9"/>
-      <c r="BE16" s="9"/>
-      <c r="BF16" s="9"/>
+        <v>231</v>
+      </c>
+      <c r="AJ16" s="10"/>
+      <c r="AK16" s="10"/>
+      <c r="AL16" s="10"/>
+      <c r="AM16" s="10"/>
+      <c r="AN16" s="10"/>
+      <c r="AO16" s="10"/>
+      <c r="AP16" s="10"/>
+      <c r="AQ16" s="10"/>
+      <c r="AR16" s="10"/>
+      <c r="AS16" s="10"/>
+      <c r="AT16" s="10"/>
+      <c r="AU16" s="10"/>
+      <c r="AV16" s="10"/>
+      <c r="AW16" s="10"/>
+      <c r="AX16" s="10"/>
+      <c r="AY16" s="10"/>
+      <c r="AZ16" s="10"/>
+      <c r="BA16" s="10"/>
+      <c r="BB16" s="10"/>
+      <c r="BC16" s="10"/>
+      <c r="BD16" s="10"/>
+      <c r="BE16" s="10"/>
+      <c r="BF16" s="10"/>
     </row>
     <row r="17">
       <c r="A17" s="3">
         <v>1.0</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>86</v>
+        <v>106</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>41</v>
+        <v>50</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>56</v>
+        <v>74</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>200</v>
+        <v>234</v>
       </c>
       <c r="F17" s="3">
         <v>2.0</v>
       </c>
-      <c r="G17" s="13">
+      <c r="G17" s="12">
         <v>0.20833333333333334</v>
       </c>
       <c r="H17" s="3">
@@ -3570,55 +3570,55 @@
         <v>2.0</v>
       </c>
       <c r="AH17" s="3" t="s">
-        <v>202</v>
+        <v>235</v>
       </c>
       <c r="AI17" s="3" t="s">
-        <v>204</v>
-      </c>
-      <c r="AJ17" s="9"/>
-      <c r="AK17" s="9"/>
-      <c r="AL17" s="9"/>
-      <c r="AM17" s="9"/>
-      <c r="AN17" s="9"/>
-      <c r="AO17" s="9"/>
-      <c r="AP17" s="9"/>
-      <c r="AQ17" s="9"/>
-      <c r="AR17" s="9"/>
-      <c r="AS17" s="9"/>
-      <c r="AT17" s="9"/>
-      <c r="AU17" s="9"/>
-      <c r="AV17" s="9"/>
-      <c r="AW17" s="9"/>
-      <c r="AX17" s="9"/>
-      <c r="AY17" s="9"/>
-      <c r="AZ17" s="9"/>
-      <c r="BA17" s="9"/>
-      <c r="BB17" s="9"/>
-      <c r="BC17" s="9"/>
-      <c r="BD17" s="9"/>
-      <c r="BE17" s="9"/>
-      <c r="BF17" s="9"/>
+        <v>236</v>
+      </c>
+      <c r="AJ17" s="10"/>
+      <c r="AK17" s="10"/>
+      <c r="AL17" s="10"/>
+      <c r="AM17" s="10"/>
+      <c r="AN17" s="10"/>
+      <c r="AO17" s="10"/>
+      <c r="AP17" s="10"/>
+      <c r="AQ17" s="10"/>
+      <c r="AR17" s="10"/>
+      <c r="AS17" s="10"/>
+      <c r="AT17" s="10"/>
+      <c r="AU17" s="10"/>
+      <c r="AV17" s="10"/>
+      <c r="AW17" s="10"/>
+      <c r="AX17" s="10"/>
+      <c r="AY17" s="10"/>
+      <c r="AZ17" s="10"/>
+      <c r="BA17" s="10"/>
+      <c r="BB17" s="10"/>
+      <c r="BC17" s="10"/>
+      <c r="BD17" s="10"/>
+      <c r="BE17" s="10"/>
+      <c r="BF17" s="10"/>
     </row>
     <row r="18">
       <c r="A18" s="3">
         <v>5.0</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>90</v>
+        <v>108</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>41</v>
+        <v>50</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>91</v>
+        <v>109</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>161</v>
+        <v>181</v>
       </c>
       <c r="F18" s="3">
         <v>2.0</v>
       </c>
-      <c r="G18" s="13">
+      <c r="G18" s="12">
         <v>0.14583333333333334</v>
       </c>
       <c r="H18" s="3">
@@ -3700,50 +3700,50 @@
         <v>1.0</v>
       </c>
       <c r="AH18" s="3" t="s">
-        <v>205</v>
+        <v>238</v>
       </c>
       <c r="AI18" s="3" t="s">
-        <v>206</v>
-      </c>
-      <c r="AJ18" s="9"/>
-      <c r="AK18" s="9"/>
-      <c r="AL18" s="9"/>
-      <c r="AM18" s="9"/>
-      <c r="AN18" s="9"/>
-      <c r="AO18" s="9"/>
-      <c r="AP18" s="9"/>
-      <c r="AQ18" s="9"/>
-      <c r="AR18" s="9"/>
-      <c r="AS18" s="9"/>
-      <c r="AT18" s="9"/>
-      <c r="AU18" s="9"/>
-      <c r="AV18" s="9"/>
-      <c r="AW18" s="9"/>
-      <c r="AX18" s="9"/>
-      <c r="AY18" s="9"/>
-      <c r="AZ18" s="9"/>
-      <c r="BA18" s="9"/>
-      <c r="BB18" s="9"/>
-      <c r="BC18" s="9"/>
-      <c r="BD18" s="9"/>
-      <c r="BE18" s="9"/>
-      <c r="BF18" s="9"/>
+        <v>239</v>
+      </c>
+      <c r="AJ18" s="10"/>
+      <c r="AK18" s="10"/>
+      <c r="AL18" s="10"/>
+      <c r="AM18" s="10"/>
+      <c r="AN18" s="10"/>
+      <c r="AO18" s="10"/>
+      <c r="AP18" s="10"/>
+      <c r="AQ18" s="10"/>
+      <c r="AR18" s="10"/>
+      <c r="AS18" s="10"/>
+      <c r="AT18" s="10"/>
+      <c r="AU18" s="10"/>
+      <c r="AV18" s="10"/>
+      <c r="AW18" s="10"/>
+      <c r="AX18" s="10"/>
+      <c r="AY18" s="10"/>
+      <c r="AZ18" s="10"/>
+      <c r="BA18" s="10"/>
+      <c r="BB18" s="10"/>
+      <c r="BC18" s="10"/>
+      <c r="BD18" s="10"/>
+      <c r="BE18" s="10"/>
+      <c r="BF18" s="10"/>
     </row>
     <row r="19">
       <c r="A19" s="3" t="s">
-        <v>197</v>
+        <v>223</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>198</v>
+        <v>224</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>199</v>
+        <v>225</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>199</v>
+        <v>225</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>199</v>
+        <v>225</v>
       </c>
       <c r="F19" s="3">
         <v>2.0</v>
@@ -3830,34 +3830,34 @@
         <v>1.38</v>
       </c>
       <c r="AH19" s="3" t="s">
-        <v>207</v>
+        <v>240</v>
       </c>
       <c r="AI19" s="3" t="s">
-        <v>208</v>
-      </c>
-      <c r="AJ19" s="9"/>
-      <c r="AK19" s="9"/>
-      <c r="AL19" s="9"/>
-      <c r="AM19" s="9"/>
-      <c r="AN19" s="9"/>
-      <c r="AO19" s="9"/>
-      <c r="AP19" s="9"/>
-      <c r="AQ19" s="9"/>
-      <c r="AR19" s="9"/>
-      <c r="AS19" s="9"/>
-      <c r="AT19" s="9"/>
-      <c r="AU19" s="9"/>
-      <c r="AV19" s="9"/>
-      <c r="AW19" s="9"/>
-      <c r="AX19" s="9"/>
-      <c r="AY19" s="9"/>
-      <c r="AZ19" s="9"/>
-      <c r="BA19" s="9"/>
-      <c r="BB19" s="9"/>
-      <c r="BC19" s="9"/>
-      <c r="BD19" s="9"/>
-      <c r="BE19" s="9"/>
-      <c r="BF19" s="9"/>
+        <v>241</v>
+      </c>
+      <c r="AJ19" s="10"/>
+      <c r="AK19" s="10"/>
+      <c r="AL19" s="10"/>
+      <c r="AM19" s="10"/>
+      <c r="AN19" s="10"/>
+      <c r="AO19" s="10"/>
+      <c r="AP19" s="10"/>
+      <c r="AQ19" s="10"/>
+      <c r="AR19" s="10"/>
+      <c r="AS19" s="10"/>
+      <c r="AT19" s="10"/>
+      <c r="AU19" s="10"/>
+      <c r="AV19" s="10"/>
+      <c r="AW19" s="10"/>
+      <c r="AX19" s="10"/>
+      <c r="AY19" s="10"/>
+      <c r="AZ19" s="10"/>
+      <c r="BA19" s="10"/>
+      <c r="BB19" s="10"/>
+      <c r="BC19" s="10"/>
+      <c r="BD19" s="10"/>
+      <c r="BE19" s="10"/>
+      <c r="BF19" s="10"/>
     </row>
   </sheetData>
   <drawing r:id="rId1"/>
@@ -3906,99 +3906,99 @@
     </row>
     <row r="3">
       <c r="A3" s="2" t="s">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="J3" s="2" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="K3" s="2" t="s">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="L3" s="2" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="M3" s="2" t="s">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="N3" s="2" t="s">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="O3" s="2" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="P3" s="2" t="s">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="Q3" s="2" t="s">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="R3" s="2" t="s">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="S3" s="2" t="s">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="T3" s="2" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="U3" s="2" t="s">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="V3" s="2" t="s">
-        <v>23</v>
+        <v>31</v>
       </c>
       <c r="W3" s="2" t="s">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="X3" s="2" t="s">
-        <v>26</v>
+        <v>33</v>
       </c>
       <c r="Y3" s="2" t="s">
-        <v>27</v>
+        <v>35</v>
       </c>
       <c r="Z3" s="2" t="s">
-        <v>28</v>
+        <v>37</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>29</v>
+        <v>41</v>
       </c>
       <c r="B4" s="3">
         <v>61.0</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>31</v>
+        <v>47</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>32</v>
+        <v>48</v>
       </c>
       <c r="F4" s="3">
         <v>2.0</v>
@@ -4066,19 +4066,19 @@
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>29</v>
+        <v>41</v>
       </c>
       <c r="B5" s="3">
         <v>10.0</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>40</v>
+        <v>49</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>41</v>
+        <v>50</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>42</v>
+        <v>51</v>
       </c>
       <c r="F5" s="3">
         <v>2.0</v>
@@ -4146,19 +4146,19 @@
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>29</v>
+        <v>41</v>
       </c>
       <c r="B6" s="3">
         <v>28.0</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>31</v>
+        <v>47</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="F6" s="3">
         <v>2.0</v>
@@ -4226,19 +4226,19 @@
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>29</v>
+        <v>41</v>
       </c>
       <c r="B7" s="3">
         <v>17.0</v>
       </c>
       <c r="C7" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="E7" s="3" t="s">
         <v>54</v>
-      </c>
-      <c r="D7" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="E7" s="3" t="s">
-        <v>50</v>
       </c>
       <c r="F7" s="3">
         <v>2.0</v>
@@ -4306,19 +4306,19 @@
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>29</v>
+        <v>41</v>
       </c>
       <c r="B8" s="3">
         <v>20.0</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>55</v>
+        <v>73</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>41</v>
+        <v>50</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>56</v>
+        <v>74</v>
       </c>
       <c r="F8" s="3">
         <v>2.0</v>
@@ -4386,19 +4386,19 @@
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>29</v>
+        <v>41</v>
       </c>
       <c r="B9" s="3">
         <v>0.0</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>59</v>
+        <v>76</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>41</v>
+        <v>50</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>42</v>
+        <v>51</v>
       </c>
       <c r="F9" s="3">
         <v>2.0</v>
@@ -4466,19 +4466,19 @@
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>29</v>
+        <v>41</v>
       </c>
       <c r="B10" s="3">
         <v>24.0</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>68</v>
+        <v>78</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>41</v>
+        <v>50</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>70</v>
+        <v>79</v>
       </c>
       <c r="F10" s="3">
         <v>2.0</v>
@@ -4546,19 +4546,19 @@
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>29</v>
+        <v>41</v>
       </c>
       <c r="B11" s="3">
         <v>7.0</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>41</v>
+        <v>50</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>56</v>
+        <v>74</v>
       </c>
       <c r="F11" s="3">
         <v>2.0</v>
@@ -4626,19 +4626,19 @@
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>29</v>
+        <v>41</v>
       </c>
       <c r="B12" s="3">
         <v>77.0</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>80</v>
+        <v>86</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>41</v>
+        <v>50</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="F12" s="3">
         <v>2.0</v>
@@ -4706,19 +4706,19 @@
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>29</v>
+        <v>41</v>
       </c>
       <c r="B13" s="3">
         <v>14.0</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>81</v>
+        <v>88</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>41</v>
+        <v>50</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>70</v>
+        <v>79</v>
       </c>
       <c r="F13" s="3">
         <v>2.0</v>
@@ -4786,19 +4786,19 @@
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>29</v>
+        <v>41</v>
       </c>
       <c r="B14" s="3">
         <v>76.0</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>41</v>
+        <v>50</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="F14" s="3">
         <v>2.0</v>
@@ -4866,19 +4866,19 @@
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>29</v>
+        <v>41</v>
       </c>
       <c r="B15" s="3">
         <v>12.0</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>84</v>
+        <v>102</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>41</v>
+        <v>50</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="F15" s="3">
         <v>2.0</v>
@@ -4946,19 +4946,19 @@
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>29</v>
+        <v>41</v>
       </c>
       <c r="B16" s="3">
         <v>1.0</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>86</v>
+        <v>106</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>41</v>
+        <v>50</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>56</v>
+        <v>74</v>
       </c>
       <c r="F16" s="3">
         <v>2.0</v>
@@ -5026,19 +5026,19 @@
     </row>
     <row r="17">
       <c r="A17" s="3" t="s">
-        <v>29</v>
+        <v>41</v>
       </c>
       <c r="B17" s="3">
         <v>5.0</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>90</v>
+        <v>108</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>41</v>
+        <v>50</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>91</v>
+        <v>109</v>
       </c>
       <c r="F17" s="3">
         <v>2.0</v>
@@ -5097,13 +5097,13 @@
       <c r="X17" s="4">
         <v>1.0</v>
       </c>
-      <c r="Y17" s="10">
+      <c r="Y17" s="14">
         <v>0.205</v>
       </c>
-      <c r="Z17" s="10">
+      <c r="Z17" s="14">
         <v>0.185</v>
       </c>
-      <c r="AA17" s="12">
+      <c r="AA17" s="15">
         <v>0.333</v>
       </c>
       <c r="AB17" s="1">
@@ -5174,167 +5174,167 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>209</v>
+        <v>77</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="s">
-        <v>210</v>
+        <v>80</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="11" t="s">
-        <v>2</v>
-      </c>
-      <c r="B4" s="11" t="s">
-        <v>3</v>
-      </c>
-      <c r="C4" s="11" t="s">
-        <v>33</v>
-      </c>
-      <c r="D4" s="11" t="s">
+      <c r="A4" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="B4" s="8" t="s">
         <v>5</v>
       </c>
-      <c r="E4" s="11" t="s">
+      <c r="C4" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="D4" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="E4" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="F4" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="G4" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="H4" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="I4" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="J4" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="K4" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="L4" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="M4" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="N4" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="O4" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="P4" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="Q4" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="R4" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="S4" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="T4" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="U4" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="F4" s="11" t="s">
-        <v>6</v>
-      </c>
-      <c r="G4" s="11" t="s">
-        <v>35</v>
-      </c>
-      <c r="H4" s="11" t="s">
+      <c r="V4" s="8" t="s">
         <v>36</v>
       </c>
-      <c r="I4" s="11" t="s">
-        <v>9</v>
-      </c>
-      <c r="J4" s="11" t="s">
-        <v>10</v>
-      </c>
-      <c r="K4" s="11" t="s">
-        <v>11</v>
-      </c>
-      <c r="L4" s="11" t="s">
+      <c r="W4" s="8" t="s">
+        <v>38</v>
+      </c>
+      <c r="X4" s="8" t="s">
+        <v>39</v>
+      </c>
+      <c r="Y4" s="8" t="s">
+        <v>40</v>
+      </c>
+      <c r="Z4" s="8" t="s">
+        <v>42</v>
+      </c>
+      <c r="AA4" s="8" t="s">
+        <v>43</v>
+      </c>
+      <c r="AB4" s="8" t="s">
+        <v>44</v>
+      </c>
+      <c r="AC4" s="8" t="s">
+        <v>45</v>
+      </c>
+      <c r="AD4" s="11" t="s">
+        <v>90</v>
+      </c>
+      <c r="AE4" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="AF4" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="AG4" s="8" t="s">
         <v>37</v>
       </c>
-      <c r="M4" s="11" t="s">
-        <v>38</v>
-      </c>
-      <c r="N4" s="11" t="s">
-        <v>39</v>
-      </c>
-      <c r="O4" s="11" t="s">
-        <v>12</v>
-      </c>
-      <c r="P4" s="11" t="s">
-        <v>13</v>
-      </c>
-      <c r="Q4" s="11" t="s">
-        <v>14</v>
-      </c>
-      <c r="R4" s="11" t="s">
-        <v>16</v>
-      </c>
-      <c r="S4" s="11" t="s">
-        <v>17</v>
-      </c>
-      <c r="T4" s="11" t="s">
-        <v>18</v>
-      </c>
-      <c r="U4" s="11" t="s">
-        <v>43</v>
-      </c>
-      <c r="V4" s="11" t="s">
-        <v>44</v>
-      </c>
-      <c r="W4" s="11" t="s">
-        <v>45</v>
-      </c>
-      <c r="X4" s="11" t="s">
-        <v>46</v>
-      </c>
-      <c r="Y4" s="11" t="s">
-        <v>47</v>
-      </c>
-      <c r="Z4" s="11" t="s">
-        <v>48</v>
-      </c>
-      <c r="AA4" s="11" t="s">
-        <v>51</v>
-      </c>
-      <c r="AB4" s="11" t="s">
-        <v>52</v>
-      </c>
-      <c r="AC4" s="11" t="s">
+      <c r="AH4" s="8" t="s">
         <v>53</v>
       </c>
-      <c r="AD4" s="14" t="s">
-        <v>95</v>
-      </c>
-      <c r="AE4" s="11" t="s">
-        <v>19</v>
-      </c>
-      <c r="AF4" s="11" t="s">
-        <v>20</v>
-      </c>
-      <c r="AG4" s="11" t="s">
-        <v>28</v>
-      </c>
-      <c r="AH4" s="11" t="s">
-        <v>57</v>
-      </c>
-      <c r="AI4" s="11" t="s">
+      <c r="AI4" s="8" t="s">
+        <v>91</v>
+      </c>
+      <c r="AJ4" s="6"/>
+      <c r="AK4" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="AL4" s="8" t="s">
+        <v>93</v>
+      </c>
+      <c r="AM4" s="8" t="s">
+        <v>94</v>
+      </c>
+      <c r="AN4" s="8" t="s">
         <v>96</v>
       </c>
-      <c r="AJ4" s="6"/>
-      <c r="AK4" s="11" t="s">
-        <v>3</v>
-      </c>
-      <c r="AL4" s="11" t="s">
+      <c r="AO4" s="8" t="s">
         <v>98</v>
       </c>
-      <c r="AM4" s="11" t="s">
+      <c r="AP4" s="8" t="s">
+        <v>99</v>
+      </c>
+      <c r="AQ4" s="8" t="s">
         <v>100</v>
       </c>
-      <c r="AN4" s="11" t="s">
+      <c r="AR4" s="6"/>
+      <c r="AS4" s="8" t="s">
+        <v>63</v>
+      </c>
+      <c r="AT4" s="8" t="s">
+        <v>93</v>
+      </c>
+      <c r="AU4" s="8" t="s">
         <v>101</v>
       </c>
-      <c r="AO4" s="11" t="s">
-        <v>102</v>
-      </c>
-      <c r="AP4" s="11" t="s">
+      <c r="AV4" s="8" t="s">
+        <v>66</v>
+      </c>
+      <c r="AW4" s="8" t="s">
+        <v>67</v>
+      </c>
+      <c r="AX4" s="8" t="s">
+        <v>68</v>
+      </c>
+      <c r="AY4" s="6"/>
+      <c r="AZ4" s="8" t="s">
         <v>103</v>
       </c>
-      <c r="AQ4" s="11" t="s">
+      <c r="BA4" s="8" t="s">
         <v>104</v>
-      </c>
-      <c r="AR4" s="6"/>
-      <c r="AS4" s="11" t="s">
-        <v>66</v>
-      </c>
-      <c r="AT4" s="11" t="s">
-        <v>98</v>
-      </c>
-      <c r="AU4" s="11" t="s">
-        <v>105</v>
-      </c>
-      <c r="AV4" s="11" t="s">
-        <v>71</v>
-      </c>
-      <c r="AW4" s="11" t="s">
-        <v>72</v>
-      </c>
-      <c r="AX4" s="11" t="s">
-        <v>73</v>
-      </c>
-      <c r="AY4" s="6"/>
-      <c r="AZ4" s="11" t="s">
-        <v>106</v>
-      </c>
-      <c r="BA4" s="11" t="s">
-        <v>107</v>
       </c>
     </row>
     <row r="5">
@@ -5342,16 +5342,16 @@
         <v>10.0</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>40</v>
+        <v>49</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>41</v>
+        <v>50</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>42</v>
+        <v>51</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>99</v>
+        <v>107</v>
       </c>
       <c r="F5" s="3">
         <v>1.0</v>
@@ -5368,7 +5368,7 @@
       <c r="J5" s="3">
         <v>17.0</v>
       </c>
-      <c r="K5" s="15">
+      <c r="K5" s="13">
         <v>0.588</v>
       </c>
       <c r="L5" s="3">
@@ -5377,7 +5377,7 @@
       <c r="M5" s="3">
         <v>7.0</v>
       </c>
-      <c r="N5" s="15">
+      <c r="N5" s="13">
         <v>0.429</v>
       </c>
       <c r="O5" s="3">
@@ -5386,7 +5386,7 @@
       <c r="P5" s="3">
         <v>10.0</v>
       </c>
-      <c r="Q5" s="15">
+      <c r="Q5" s="13">
         <v>0.7</v>
       </c>
       <c r="R5" s="3">
@@ -5395,7 +5395,7 @@
       <c r="S5" s="3">
         <v>0.0</v>
       </c>
-      <c r="T5" s="15">
+      <c r="T5" s="13">
         <v>0.0</v>
       </c>
       <c r="U5" s="3">
@@ -5425,26 +5425,26 @@
       <c r="AC5" s="3">
         <v>27.0</v>
       </c>
-      <c r="AD5" s="8">
+      <c r="AD5" s="9">
         <v>18</v>
       </c>
-      <c r="AE5" s="15">
+      <c r="AE5" s="13">
         <v>0.794</v>
       </c>
-      <c r="AF5" s="15">
+      <c r="AF5" s="13">
         <v>0.794</v>
       </c>
       <c r="AG5" s="3">
         <v>1.5</v>
       </c>
       <c r="AH5" s="3" t="s">
-        <v>146</v>
+        <v>113</v>
       </c>
       <c r="AI5" s="3" t="s">
-        <v>211</v>
+        <v>114</v>
       </c>
       <c r="AK5" s="3" t="s">
-        <v>152</v>
+        <v>116</v>
       </c>
       <c r="AL5" s="7">
         <v>1.51875</v>
@@ -5455,22 +5455,22 @@
       <c r="AN5" s="3">
         <v>112.0</v>
       </c>
-      <c r="AO5" s="8">
+      <c r="AO5" s="9">
         <v>14.5</v>
       </c>
       <c r="AP5" s="3">
         <v>-8.5</v>
       </c>
-      <c r="AQ5" s="8">
+      <c r="AQ5" s="9">
         <v>23</v>
       </c>
       <c r="AS5" s="3" t="s">
         <v>120</v>
       </c>
-      <c r="AT5" s="13">
+      <c r="AT5" s="12">
         <v>0.78125</v>
       </c>
-      <c r="AU5" s="8">
+      <c r="AU5" s="9">
         <v>16</v>
       </c>
       <c r="AV5" s="3">
@@ -5479,14 +5479,14 @@
       <c r="AW5" s="3">
         <v>108.5</v>
       </c>
-      <c r="AX5" s="8">
+      <c r="AX5" s="9">
         <v>23.5</v>
       </c>
       <c r="AZ5" s="3" t="s">
-        <v>212</v>
+        <v>123</v>
       </c>
       <c r="BA5" s="3" t="s">
-        <v>213</v>
+        <v>124</v>
       </c>
     </row>
     <row r="6">
@@ -5494,16 +5494,16 @@
         <v>61.0</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>31</v>
+        <v>47</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>32</v>
+        <v>48</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="F6" s="3">
         <v>1.0</v>
@@ -5520,7 +5520,7 @@
       <c r="J6" s="3">
         <v>18.0</v>
       </c>
-      <c r="K6" s="15">
+      <c r="K6" s="13">
         <v>0.556</v>
       </c>
       <c r="L6" s="3">
@@ -5529,7 +5529,7 @@
       <c r="M6" s="3">
         <v>14.0</v>
       </c>
-      <c r="N6" s="15">
+      <c r="N6" s="13">
         <v>0.714</v>
       </c>
       <c r="O6" s="3">
@@ -5538,7 +5538,7 @@
       <c r="P6" s="3">
         <v>4.0</v>
       </c>
-      <c r="Q6" s="15">
+      <c r="Q6" s="13">
         <v>0.0</v>
       </c>
       <c r="R6" s="3">
@@ -5547,7 +5547,7 @@
       <c r="S6" s="3">
         <v>3.0</v>
       </c>
-      <c r="T6" s="15">
+      <c r="T6" s="13">
         <v>0.667</v>
       </c>
       <c r="U6" s="3">
@@ -5577,26 +5577,26 @@
       <c r="AC6" s="3">
         <v>23.0</v>
       </c>
-      <c r="AD6" s="8">
+      <c r="AD6" s="9">
         <v>13</v>
       </c>
-      <c r="AE6" s="15">
+      <c r="AE6" s="13">
         <v>0.556</v>
       </c>
-      <c r="AF6" s="15">
+      <c r="AF6" s="13">
         <v>0.569</v>
       </c>
       <c r="AG6" s="3">
         <v>2.0</v>
       </c>
       <c r="AH6" s="3" t="s">
-        <v>214</v>
+        <v>128</v>
       </c>
       <c r="AI6" s="3" t="s">
-        <v>215</v>
+        <v>130</v>
       </c>
       <c r="AK6" s="3" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="AL6" s="7">
         <v>1.3576388888888888</v>
@@ -5607,22 +5607,22 @@
       <c r="AN6" s="3">
         <v>113.5</v>
       </c>
-      <c r="AO6" s="8">
+      <c r="AO6" s="9">
         <v>11.5</v>
       </c>
       <c r="AP6" s="3">
         <v>-6.0</v>
       </c>
-      <c r="AQ6" s="8">
+      <c r="AQ6" s="9">
         <v>17.5</v>
       </c>
       <c r="AS6" s="3" t="s">
-        <v>216</v>
-      </c>
-      <c r="AT6" s="13">
+        <v>133</v>
+      </c>
+      <c r="AT6" s="12">
         <v>0.5138888888888888</v>
       </c>
-      <c r="AU6" s="8">
+      <c r="AU6" s="9">
         <v>8</v>
       </c>
       <c r="AV6" s="3">
@@ -5631,14 +5631,14 @@
       <c r="AW6" s="3">
         <v>112.0</v>
       </c>
-      <c r="AX6" s="8">
+      <c r="AX6" s="9">
         <v>14</v>
       </c>
       <c r="AZ6" s="3" t="s">
-        <v>217</v>
+        <v>135</v>
       </c>
       <c r="BA6" s="3" t="s">
-        <v>218</v>
+        <v>137</v>
       </c>
     </row>
     <row r="7">
@@ -5646,21 +5646,21 @@
         <v>17.0</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>135</v>
+        <v>140</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>31</v>
+        <v>47</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>136</v>
+        <v>142</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="F7" s="3">
         <v>1.0</v>
       </c>
-      <c r="G7" s="13">
+      <c r="G7" s="12">
         <v>0.9666666666666667</v>
       </c>
       <c r="H7" s="3">
@@ -5672,7 +5672,7 @@
       <c r="J7" s="3">
         <v>8.0</v>
       </c>
-      <c r="K7" s="15">
+      <c r="K7" s="13">
         <v>0.625</v>
       </c>
       <c r="L7" s="3">
@@ -5681,7 +5681,7 @@
       <c r="M7" s="3">
         <v>8.0</v>
       </c>
-      <c r="N7" s="15">
+      <c r="N7" s="13">
         <v>0.625</v>
       </c>
       <c r="O7" s="3">
@@ -5690,7 +5690,7 @@
       <c r="P7" s="3">
         <v>0.0</v>
       </c>
-      <c r="Q7" s="15">
+      <c r="Q7" s="13">
         <v>0.0</v>
       </c>
       <c r="R7" s="3">
@@ -5699,7 +5699,7 @@
       <c r="S7" s="3">
         <v>5.0</v>
       </c>
-      <c r="T7" s="15">
+      <c r="T7" s="13">
         <v>1.0</v>
       </c>
       <c r="U7" s="3">
@@ -5732,23 +5732,23 @@
       <c r="AD7" s="3">
         <v>-13.0</v>
       </c>
-      <c r="AE7" s="15">
+      <c r="AE7" s="13">
         <v>0.625</v>
       </c>
-      <c r="AF7" s="15">
+      <c r="AF7" s="13">
         <v>0.735</v>
       </c>
       <c r="AG7" s="3">
         <v>0.0</v>
       </c>
       <c r="AH7" s="3" t="s">
-        <v>190</v>
+        <v>144</v>
       </c>
       <c r="AI7" s="3" t="s">
-        <v>219</v>
+        <v>145</v>
       </c>
       <c r="AK7" s="3" t="s">
-        <v>119</v>
+        <v>132</v>
       </c>
       <c r="AL7" s="7">
         <v>1.1222222222222222</v>
@@ -5759,19 +5759,19 @@
       <c r="AN7" s="3">
         <v>114.5</v>
       </c>
-      <c r="AO7" s="8">
+      <c r="AO7" s="9">
         <v>9.5</v>
       </c>
       <c r="AP7" s="3">
         <v>-4.0</v>
       </c>
-      <c r="AQ7" s="8">
+      <c r="AQ7" s="9">
         <v>13.5</v>
       </c>
       <c r="AS7" s="3" t="s">
-        <v>220</v>
-      </c>
-      <c r="AT7" s="13">
+        <v>151</v>
+      </c>
+      <c r="AT7" s="12">
         <v>0.34375</v>
       </c>
       <c r="AU7" s="3">
@@ -5787,10 +5787,10 @@
         <v>-25.5</v>
       </c>
       <c r="AZ7" s="3" t="s">
-        <v>143</v>
+        <v>152</v>
       </c>
       <c r="BA7" s="3" t="s">
-        <v>221</v>
+        <v>153</v>
       </c>
     </row>
     <row r="8">
@@ -5798,21 +5798,21 @@
         <v>28.0</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>31</v>
+        <v>47</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="F8" s="3">
         <v>1.0</v>
       </c>
-      <c r="G8" s="13">
+      <c r="G8" s="12">
         <v>0.7715277777777778</v>
       </c>
       <c r="H8" s="3">
@@ -5824,7 +5824,7 @@
       <c r="J8" s="3">
         <v>8.0</v>
       </c>
-      <c r="K8" s="15">
+      <c r="K8" s="13">
         <v>0.5</v>
       </c>
       <c r="L8" s="3">
@@ -5833,7 +5833,7 @@
       <c r="M8" s="3">
         <v>4.0</v>
       </c>
-      <c r="N8" s="15">
+      <c r="N8" s="13">
         <v>0.5</v>
       </c>
       <c r="O8" s="3">
@@ -5842,7 +5842,7 @@
       <c r="P8" s="3">
         <v>4.0</v>
       </c>
-      <c r="Q8" s="15">
+      <c r="Q8" s="13">
         <v>0.5</v>
       </c>
       <c r="R8" s="3">
@@ -5851,7 +5851,7 @@
       <c r="S8" s="3">
         <v>8.0</v>
       </c>
-      <c r="T8" s="15">
+      <c r="T8" s="13">
         <v>0.625</v>
       </c>
       <c r="U8" s="3">
@@ -5884,23 +5884,23 @@
       <c r="AD8" s="3">
         <v>-11.0</v>
       </c>
-      <c r="AE8" s="15">
+      <c r="AE8" s="13">
         <v>0.625</v>
       </c>
-      <c r="AF8" s="15">
+      <c r="AF8" s="13">
         <v>0.651</v>
       </c>
       <c r="AG8" s="3">
         <v>0.33</v>
       </c>
       <c r="AH8" s="3" t="s">
-        <v>117</v>
+        <v>129</v>
       </c>
       <c r="AI8" s="3" t="s">
-        <v>222</v>
+        <v>156</v>
       </c>
       <c r="AK8" s="3" t="s">
-        <v>92</v>
+        <v>87</v>
       </c>
       <c r="AL8" s="7">
         <v>1.1597222222222223</v>
@@ -5911,13 +5911,13 @@
       <c r="AN8" s="3">
         <v>115.0</v>
       </c>
-      <c r="AO8" s="8">
+      <c r="AO8" s="9">
         <v>7.5</v>
       </c>
       <c r="AP8" s="3">
         <v>-2.5</v>
       </c>
-      <c r="AQ8" s="8">
+      <c r="AQ8" s="9">
         <v>10</v>
       </c>
     </row>
@@ -5926,16 +5926,16 @@
         <v>20.0</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>145</v>
+        <v>161</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>31</v>
+        <v>47</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>136</v>
+        <v>142</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="F9" s="3">
         <v>1.0</v>
@@ -5952,7 +5952,7 @@
       <c r="J9" s="3">
         <v>13.0</v>
       </c>
-      <c r="K9" s="15">
+      <c r="K9" s="13">
         <v>0.385</v>
       </c>
       <c r="L9" s="3">
@@ -5961,7 +5961,7 @@
       <c r="M9" s="3">
         <v>9.0</v>
       </c>
-      <c r="N9" s="15">
+      <c r="N9" s="13">
         <v>0.444</v>
       </c>
       <c r="O9" s="3">
@@ -5970,7 +5970,7 @@
       <c r="P9" s="3">
         <v>4.0</v>
       </c>
-      <c r="Q9" s="15">
+      <c r="Q9" s="13">
         <v>0.25</v>
       </c>
       <c r="R9" s="3">
@@ -5979,7 +5979,7 @@
       <c r="S9" s="3">
         <v>4.0</v>
       </c>
-      <c r="T9" s="15">
+      <c r="T9" s="13">
         <v>0.75</v>
       </c>
       <c r="U9" s="3">
@@ -6009,26 +6009,26 @@
       <c r="AC9" s="3">
         <v>29.0</v>
       </c>
-      <c r="AD9" s="8">
+      <c r="AD9" s="9">
         <v>21</v>
       </c>
-      <c r="AE9" s="15">
+      <c r="AE9" s="13">
         <v>0.423</v>
       </c>
-      <c r="AF9" s="15">
+      <c r="AF9" s="13">
         <v>0.474</v>
       </c>
       <c r="AG9" s="3">
         <v>1.67</v>
       </c>
       <c r="AH9" s="3" t="s">
-        <v>223</v>
+        <v>164</v>
       </c>
       <c r="AI9" s="3" t="s">
-        <v>224</v>
+        <v>166</v>
       </c>
       <c r="AK9" s="3" t="s">
-        <v>131</v>
+        <v>139</v>
       </c>
       <c r="AL9" s="7">
         <v>1.7034722222222223</v>
@@ -6039,13 +6039,13 @@
       <c r="AN9" s="3">
         <v>116.5</v>
       </c>
-      <c r="AO9" s="8">
+      <c r="AO9" s="9">
         <v>4.5</v>
       </c>
-      <c r="AP9" s="8">
+      <c r="AP9" s="9">
         <v>2</v>
       </c>
-      <c r="AQ9" s="8">
+      <c r="AQ9" s="9">
         <v>2.5</v>
       </c>
     </row>
@@ -6054,16 +6054,16 @@
         <v>0.0</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>59</v>
+        <v>76</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>41</v>
+        <v>50</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>150</v>
+        <v>169</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>99</v>
+        <v>107</v>
       </c>
       <c r="F10" s="3">
         <v>1.0</v>
@@ -6080,7 +6080,7 @@
       <c r="J10" s="3">
         <v>12.0</v>
       </c>
-      <c r="K10" s="15">
+      <c r="K10" s="13">
         <v>0.5</v>
       </c>
       <c r="L10" s="3">
@@ -6089,7 +6089,7 @@
       <c r="M10" s="3">
         <v>7.0</v>
       </c>
-      <c r="N10" s="15">
+      <c r="N10" s="13">
         <v>0.714</v>
       </c>
       <c r="O10" s="3">
@@ -6098,7 +6098,7 @@
       <c r="P10" s="3">
         <v>5.0</v>
       </c>
-      <c r="Q10" s="15">
+      <c r="Q10" s="13">
         <v>0.2</v>
       </c>
       <c r="R10" s="3">
@@ -6107,7 +6107,7 @@
       <c r="S10" s="3">
         <v>0.0</v>
       </c>
-      <c r="T10" s="15">
+      <c r="T10" s="13">
         <v>0.0</v>
       </c>
       <c r="U10" s="3">
@@ -6137,28 +6137,28 @@
       <c r="AC10" s="3">
         <v>18.0</v>
       </c>
-      <c r="AD10" s="8">
+      <c r="AD10" s="9">
         <v>14</v>
       </c>
-      <c r="AE10" s="15">
+      <c r="AE10" s="13">
         <v>0.542</v>
       </c>
-      <c r="AF10" s="15">
+      <c r="AF10" s="13">
         <v>0.542</v>
       </c>
       <c r="AG10" s="3">
         <v>1.2</v>
       </c>
       <c r="AH10" s="3" t="s">
-        <v>225</v>
+        <v>176</v>
       </c>
       <c r="AI10" s="3" t="s">
-        <v>226</v>
+        <v>177</v>
       </c>
       <c r="AK10" s="3" t="s">
-        <v>115</v>
-      </c>
-      <c r="AL10" s="13">
+        <v>118</v>
+      </c>
+      <c r="AL10" s="12">
         <v>0.9652777777777778</v>
       </c>
       <c r="AM10" s="3">
@@ -6170,7 +6170,7 @@
       <c r="AO10" s="3">
         <v>-2.5</v>
       </c>
-      <c r="AP10" s="8">
+      <c r="AP10" s="9">
         <v>8.5</v>
       </c>
       <c r="AQ10" s="3">
@@ -6182,21 +6182,21 @@
         <v>24.0</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>159</v>
+        <v>180</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>41</v>
+        <v>50</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>91</v>
+        <v>109</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>161</v>
+        <v>181</v>
       </c>
       <c r="F11" s="3">
         <v>1.0</v>
       </c>
-      <c r="G11" s="13">
+      <c r="G11" s="12">
         <v>0.9652777777777778</v>
       </c>
       <c r="H11" s="3">
@@ -6208,7 +6208,7 @@
       <c r="J11" s="3">
         <v>8.0</v>
       </c>
-      <c r="K11" s="15">
+      <c r="K11" s="13">
         <v>0.5</v>
       </c>
       <c r="L11" s="3">
@@ -6217,7 +6217,7 @@
       <c r="M11" s="3">
         <v>2.0</v>
       </c>
-      <c r="N11" s="15">
+      <c r="N11" s="13">
         <v>0.0</v>
       </c>
       <c r="O11" s="3">
@@ -6226,7 +6226,7 @@
       <c r="P11" s="3">
         <v>6.0</v>
       </c>
-      <c r="Q11" s="15">
+      <c r="Q11" s="13">
         <v>0.667</v>
       </c>
       <c r="R11" s="3">
@@ -6235,7 +6235,7 @@
       <c r="S11" s="3">
         <v>0.0</v>
       </c>
-      <c r="T11" s="15">
+      <c r="T11" s="13">
         <v>0.0</v>
       </c>
       <c r="U11" s="3">
@@ -6268,25 +6268,25 @@
       <c r="AD11" s="3">
         <v>-4.0</v>
       </c>
-      <c r="AE11" s="15">
+      <c r="AE11" s="13">
         <v>0.75</v>
       </c>
-      <c r="AF11" s="15">
+      <c r="AF11" s="13">
         <v>0.75</v>
       </c>
       <c r="AG11" s="3">
         <v>2.0</v>
       </c>
       <c r="AH11" s="3" t="s">
-        <v>227</v>
+        <v>183</v>
       </c>
       <c r="AI11" s="3" t="s">
-        <v>228</v>
+        <v>184</v>
       </c>
       <c r="AK11" s="3" t="s">
-        <v>148</v>
-      </c>
-      <c r="AL11" s="13">
+        <v>165</v>
+      </c>
+      <c r="AL11" s="12">
         <v>0.7715277777777778</v>
       </c>
       <c r="AM11" s="3">
@@ -6298,7 +6298,7 @@
       <c r="AO11" s="3">
         <v>-8.5</v>
       </c>
-      <c r="AP11" s="8">
+      <c r="AP11" s="9">
         <v>11</v>
       </c>
       <c r="AQ11" s="3">
@@ -6310,16 +6310,16 @@
         <v>7.0</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>55</v>
+        <v>73</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>41</v>
+        <v>50</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>166</v>
+        <v>189</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>99</v>
+        <v>107</v>
       </c>
       <c r="F12" s="3">
         <v>1.0</v>
@@ -6336,7 +6336,7 @@
       <c r="J12" s="3">
         <v>6.0</v>
       </c>
-      <c r="K12" s="15">
+      <c r="K12" s="13">
         <v>0.5</v>
       </c>
       <c r="L12" s="3">
@@ -6345,7 +6345,7 @@
       <c r="M12" s="3">
         <v>5.0</v>
       </c>
-      <c r="N12" s="15">
+      <c r="N12" s="13">
         <v>0.4</v>
       </c>
       <c r="O12" s="3">
@@ -6354,7 +6354,7 @@
       <c r="P12" s="3">
         <v>1.0</v>
       </c>
-      <c r="Q12" s="15">
+      <c r="Q12" s="13">
         <v>1.0</v>
       </c>
       <c r="R12" s="3">
@@ -6363,7 +6363,7 @@
       <c r="S12" s="3">
         <v>0.0</v>
       </c>
-      <c r="T12" s="15">
+      <c r="T12" s="13">
         <v>0.0</v>
       </c>
       <c r="U12" s="3">
@@ -6393,28 +6393,28 @@
       <c r="AC12" s="3">
         <v>10.0</v>
       </c>
-      <c r="AD12" s="8">
+      <c r="AD12" s="9">
         <v>17</v>
       </c>
-      <c r="AE12" s="15">
+      <c r="AE12" s="13">
         <v>0.583</v>
       </c>
-      <c r="AF12" s="15">
+      <c r="AF12" s="13">
         <v>0.583</v>
       </c>
       <c r="AG12" s="3">
         <v>2.0</v>
       </c>
       <c r="AH12" s="3" t="s">
-        <v>229</v>
+        <v>193</v>
       </c>
       <c r="AI12" s="3" t="s">
-        <v>230</v>
+        <v>194</v>
       </c>
       <c r="AK12" s="3" t="s">
-        <v>156</v>
-      </c>
-      <c r="AL12" s="13">
+        <v>173</v>
+      </c>
+      <c r="AL12" s="12">
         <v>0.9666666666666667</v>
       </c>
       <c r="AM12" s="3">
@@ -6426,7 +6426,7 @@
       <c r="AO12" s="3">
         <v>-11.5</v>
       </c>
-      <c r="AP12" s="8">
+      <c r="AP12" s="9">
         <v>12.5</v>
       </c>
       <c r="AQ12" s="3">
@@ -6438,21 +6438,21 @@
         <v>77.0</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>176</v>
+        <v>197</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>41</v>
+        <v>50</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>91</v>
+        <v>109</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>161</v>
+        <v>181</v>
       </c>
       <c r="F13" s="3">
         <v>1.0</v>
       </c>
-      <c r="G13" s="13">
+      <c r="G13" s="12">
         <v>0.4388888888888889</v>
       </c>
       <c r="H13" s="3">
@@ -6464,7 +6464,7 @@
       <c r="J13" s="3">
         <v>2.0</v>
       </c>
-      <c r="K13" s="15">
+      <c r="K13" s="13">
         <v>1.0</v>
       </c>
       <c r="L13" s="3">
@@ -6473,7 +6473,7 @@
       <c r="M13" s="3">
         <v>1.0</v>
       </c>
-      <c r="N13" s="15">
+      <c r="N13" s="13">
         <v>1.0</v>
       </c>
       <c r="O13" s="3">
@@ -6482,7 +6482,7 @@
       <c r="P13" s="3">
         <v>1.0</v>
       </c>
-      <c r="Q13" s="15">
+      <c r="Q13" s="13">
         <v>1.0</v>
       </c>
       <c r="R13" s="3">
@@ -6491,7 +6491,7 @@
       <c r="S13" s="3">
         <v>0.0</v>
       </c>
-      <c r="T13" s="15">
+      <c r="T13" s="13">
         <v>0.0</v>
       </c>
       <c r="U13" s="3">
@@ -6524,20 +6524,20 @@
       <c r="AD13" s="3">
         <v>-5.0</v>
       </c>
-      <c r="AE13" s="15">
+      <c r="AE13" s="13">
         <v>1.25</v>
       </c>
-      <c r="AF13" s="15">
+      <c r="AF13" s="13">
         <v>1.25</v>
       </c>
       <c r="AG13" s="3">
         <v>0.0</v>
       </c>
       <c r="AH13" s="3" t="s">
-        <v>179</v>
+        <v>202</v>
       </c>
       <c r="AI13" s="3" t="s">
-        <v>231</v>
+        <v>204</v>
       </c>
     </row>
     <row r="14">
@@ -6545,21 +6545,21 @@
         <v>76.0</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>80</v>
+        <v>86</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>41</v>
+        <v>50</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>173</v>
+        <v>196</v>
       </c>
       <c r="F14" s="3">
         <v>1.0</v>
       </c>
-      <c r="G14" s="13">
+      <c r="G14" s="12">
         <v>0.46944444444444444</v>
       </c>
       <c r="H14" s="3">
@@ -6571,7 +6571,7 @@
       <c r="J14" s="3">
         <v>6.0</v>
       </c>
-      <c r="K14" s="15">
+      <c r="K14" s="13">
         <v>0.333</v>
       </c>
       <c r="L14" s="3">
@@ -6580,7 +6580,7 @@
       <c r="M14" s="3">
         <v>4.0</v>
       </c>
-      <c r="N14" s="15">
+      <c r="N14" s="13">
         <v>0.5</v>
       </c>
       <c r="O14" s="3">
@@ -6589,7 +6589,7 @@
       <c r="P14" s="3">
         <v>2.0</v>
       </c>
-      <c r="Q14" s="15">
+      <c r="Q14" s="13">
         <v>0.0</v>
       </c>
       <c r="R14" s="3">
@@ -6598,7 +6598,7 @@
       <c r="S14" s="3">
         <v>0.0</v>
       </c>
-      <c r="T14" s="15">
+      <c r="T14" s="13">
         <v>0.0</v>
       </c>
       <c r="U14" s="3">
@@ -6631,20 +6631,20 @@
       <c r="AD14" s="3">
         <v>-10.0</v>
       </c>
-      <c r="AE14" s="15">
+      <c r="AE14" s="13">
         <v>0.333</v>
       </c>
-      <c r="AF14" s="15">
+      <c r="AF14" s="13">
         <v>0.333</v>
       </c>
       <c r="AG14" s="3">
         <v>0.0</v>
       </c>
       <c r="AH14" s="3" t="s">
-        <v>232</v>
+        <v>208</v>
       </c>
       <c r="AI14" s="3" t="s">
-        <v>233</v>
+        <v>210</v>
       </c>
     </row>
     <row r="15">
@@ -6652,21 +6652,21 @@
         <v>14.0</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>189</v>
+        <v>213</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>41</v>
+        <v>50</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>32</v>
+        <v>48</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="F15" s="3">
         <v>1.0</v>
       </c>
-      <c r="G15" s="13">
+      <c r="G15" s="12">
         <v>0.21319444444444444</v>
       </c>
       <c r="H15" s="3">
@@ -6678,7 +6678,7 @@
       <c r="J15" s="3">
         <v>1.0</v>
       </c>
-      <c r="K15" s="15">
+      <c r="K15" s="13">
         <v>1.0</v>
       </c>
       <c r="L15" s="3">
@@ -6687,7 +6687,7 @@
       <c r="M15" s="3">
         <v>1.0</v>
       </c>
-      <c r="N15" s="15">
+      <c r="N15" s="13">
         <v>1.0</v>
       </c>
       <c r="O15" s="3">
@@ -6696,7 +6696,7 @@
       <c r="P15" s="3">
         <v>0.0</v>
       </c>
-      <c r="Q15" s="15">
+      <c r="Q15" s="13">
         <v>0.0</v>
       </c>
       <c r="R15" s="3">
@@ -6705,7 +6705,7 @@
       <c r="S15" s="3">
         <v>0.0</v>
       </c>
-      <c r="T15" s="15">
+      <c r="T15" s="13">
         <v>0.0</v>
       </c>
       <c r="U15" s="3">
@@ -6735,23 +6735,23 @@
       <c r="AC15" s="3">
         <v>2.0</v>
       </c>
-      <c r="AD15" s="8">
+      <c r="AD15" s="9">
         <v>11</v>
       </c>
-      <c r="AE15" s="15">
-        <v>1.0</v>
-      </c>
-      <c r="AF15" s="15">
+      <c r="AE15" s="13">
+        <v>1.0</v>
+      </c>
+      <c r="AF15" s="13">
         <v>1.0</v>
       </c>
       <c r="AG15" s="3">
         <v>0.0</v>
       </c>
       <c r="AH15" s="3" t="s">
-        <v>234</v>
+        <v>216</v>
       </c>
       <c r="AI15" s="3" t="s">
-        <v>235</v>
+        <v>217</v>
       </c>
     </row>
     <row r="16">
@@ -6759,21 +6759,21 @@
         <v>12.0</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>171</v>
+        <v>192</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>41</v>
+        <v>50</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>32</v>
+        <v>48</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>172</v>
+        <v>195</v>
       </c>
       <c r="F16" s="3">
         <v>1.0</v>
       </c>
-      <c r="G16" s="13">
+      <c r="G16" s="12">
         <v>0.1361111111111111</v>
       </c>
       <c r="H16" s="3">
@@ -6785,7 +6785,7 @@
       <c r="J16" s="3">
         <v>0.0</v>
       </c>
-      <c r="K16" s="15">
+      <c r="K16" s="13">
         <v>0.0</v>
       </c>
       <c r="L16" s="3">
@@ -6794,7 +6794,7 @@
       <c r="M16" s="3">
         <v>0.0</v>
       </c>
-      <c r="N16" s="15">
+      <c r="N16" s="13">
         <v>0.0</v>
       </c>
       <c r="O16" s="3">
@@ -6803,7 +6803,7 @@
       <c r="P16" s="3">
         <v>0.0</v>
       </c>
-      <c r="Q16" s="15">
+      <c r="Q16" s="13">
         <v>0.0</v>
       </c>
       <c r="R16" s="3">
@@ -6812,7 +6812,7 @@
       <c r="S16" s="3">
         <v>0.0</v>
       </c>
-      <c r="T16" s="15">
+      <c r="T16" s="13">
         <v>0.0</v>
       </c>
       <c r="U16" s="3">
@@ -6845,20 +6845,20 @@
       <c r="AD16" s="3">
         <v>-9.0</v>
       </c>
-      <c r="AE16" s="15">
-        <v>0.0</v>
-      </c>
-      <c r="AF16" s="15">
+      <c r="AE16" s="13">
+        <v>0.0</v>
+      </c>
+      <c r="AF16" s="13">
         <v>0.0</v>
       </c>
       <c r="AG16" s="3">
         <v>0.0</v>
       </c>
       <c r="AH16" s="3" t="s">
-        <v>236</v>
+        <v>221</v>
       </c>
       <c r="AI16" s="3" t="s">
-        <v>237</v>
+        <v>222</v>
       </c>
     </row>
     <row r="17">
@@ -6866,21 +6866,21 @@
         <v>1.0</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>186</v>
+        <v>209</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>41</v>
+        <v>50</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>32</v>
+        <v>48</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>181</v>
+        <v>205</v>
       </c>
       <c r="F17" s="3">
         <v>1.0</v>
       </c>
-      <c r="G17" s="13">
+      <c r="G17" s="12">
         <v>0.15833333333333333</v>
       </c>
       <c r="H17" s="3">
@@ -6892,7 +6892,7 @@
       <c r="J17" s="3">
         <v>0.0</v>
       </c>
-      <c r="K17" s="15">
+      <c r="K17" s="13">
         <v>0.0</v>
       </c>
       <c r="L17" s="3">
@@ -6901,7 +6901,7 @@
       <c r="M17" s="3">
         <v>0.0</v>
       </c>
-      <c r="N17" s="15">
+      <c r="N17" s="13">
         <v>0.0</v>
       </c>
       <c r="O17" s="3">
@@ -6910,7 +6910,7 @@
       <c r="P17" s="3">
         <v>0.0</v>
       </c>
-      <c r="Q17" s="15">
+      <c r="Q17" s="13">
         <v>0.0</v>
       </c>
       <c r="R17" s="3">
@@ -6919,7 +6919,7 @@
       <c r="S17" s="3">
         <v>0.0</v>
       </c>
-      <c r="T17" s="15">
+      <c r="T17" s="13">
         <v>0.0</v>
       </c>
       <c r="U17" s="3">
@@ -6952,20 +6952,20 @@
       <c r="AD17" s="3">
         <v>-7.0</v>
       </c>
-      <c r="AE17" s="15">
-        <v>0.0</v>
-      </c>
-      <c r="AF17" s="15">
+      <c r="AE17" s="13">
+        <v>0.0</v>
+      </c>
+      <c r="AF17" s="13">
         <v>0.0</v>
       </c>
       <c r="AG17" s="3">
         <v>0.0</v>
       </c>
       <c r="AH17" s="3" t="s">
-        <v>236</v>
+        <v>221</v>
       </c>
       <c r="AI17" s="3" t="s">
-        <v>238</v>
+        <v>229</v>
       </c>
     </row>
     <row r="18">
@@ -6973,21 +6973,21 @@
         <v>5.0</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>90</v>
+        <v>108</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>41</v>
+        <v>50</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>91</v>
+        <v>109</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>161</v>
+        <v>181</v>
       </c>
       <c r="F18" s="3">
         <v>1.0</v>
       </c>
-      <c r="G18" s="13">
+      <c r="G18" s="12">
         <v>0.06041666666666667</v>
       </c>
       <c r="H18" s="3">
@@ -6999,7 +6999,7 @@
       <c r="J18" s="3">
         <v>0.0</v>
       </c>
-      <c r="K18" s="15">
+      <c r="K18" s="13">
         <v>0.0</v>
       </c>
       <c r="L18" s="3">
@@ -7008,7 +7008,7 @@
       <c r="M18" s="3">
         <v>0.0</v>
       </c>
-      <c r="N18" s="15">
+      <c r="N18" s="13">
         <v>0.0</v>
       </c>
       <c r="O18" s="3">
@@ -7017,7 +7017,7 @@
       <c r="P18" s="3">
         <v>0.0</v>
       </c>
-      <c r="Q18" s="15">
+      <c r="Q18" s="13">
         <v>0.0</v>
       </c>
       <c r="R18" s="3">
@@ -7026,7 +7026,7 @@
       <c r="S18" s="3">
         <v>0.0</v>
       </c>
-      <c r="T18" s="15">
+      <c r="T18" s="13">
         <v>0.0</v>
       </c>
       <c r="U18" s="3">
@@ -7059,37 +7059,37 @@
       <c r="AD18" s="3">
         <v>-10.0</v>
       </c>
-      <c r="AE18" s="15">
-        <v>0.0</v>
-      </c>
-      <c r="AF18" s="15">
+      <c r="AE18" s="13">
+        <v>0.0</v>
+      </c>
+      <c r="AF18" s="13">
         <v>0.0</v>
       </c>
       <c r="AG18" s="3">
         <v>0.0</v>
       </c>
       <c r="AH18" s="3" t="s">
-        <v>239</v>
+        <v>232</v>
       </c>
       <c r="AI18" s="3" t="s">
-        <v>240</v>
+        <v>233</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="3" t="s">
-        <v>197</v>
+        <v>223</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>198</v>
+        <v>224</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>199</v>
+        <v>225</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>199</v>
+        <v>225</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>199</v>
+        <v>225</v>
       </c>
       <c r="F19" s="3">
         <v>1.0</v>
@@ -7106,7 +7106,7 @@
       <c r="J19" s="3">
         <v>99.0</v>
       </c>
-      <c r="K19" s="15">
+      <c r="K19" s="13">
         <v>0.495</v>
       </c>
       <c r="L19" s="3">
@@ -7115,7 +7115,7 @@
       <c r="M19" s="3">
         <v>62.0</v>
       </c>
-      <c r="N19" s="15">
+      <c r="N19" s="13">
         <v>0.565</v>
       </c>
       <c r="O19" s="3">
@@ -7124,7 +7124,7 @@
       <c r="P19" s="3">
         <v>37.0</v>
       </c>
-      <c r="Q19" s="15">
+      <c r="Q19" s="13">
         <v>0.459</v>
       </c>
       <c r="R19" s="3">
@@ -7133,7 +7133,7 @@
       <c r="S19" s="3">
         <v>20.0</v>
       </c>
-      <c r="T19" s="15">
+      <c r="T19" s="13">
         <v>0.75</v>
       </c>
       <c r="U19" s="3">
@@ -7163,23 +7163,23 @@
       <c r="AC19" s="3">
         <v>165.0</v>
       </c>
-      <c r="AD19" s="8">
+      <c r="AD19" s="9">
         <v>3</v>
       </c>
-      <c r="AE19" s="15">
+      <c r="AE19" s="13">
         <v>0.581</v>
       </c>
-      <c r="AF19" s="15">
+      <c r="AF19" s="13">
         <v>0.631</v>
       </c>
       <c r="AG19" s="3">
         <v>1.24</v>
       </c>
       <c r="AH19" s="3" t="s">
-        <v>201</v>
+        <v>227</v>
       </c>
       <c r="AI19" s="3" t="s">
-        <v>241</v>
+        <v>237</v>
       </c>
     </row>
   </sheetData>
@@ -7246,167 +7246,167 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="s">
-        <v>87</v>
+        <v>82</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="11" t="s">
-        <v>2</v>
-      </c>
-      <c r="B4" s="11" t="s">
-        <v>3</v>
-      </c>
-      <c r="C4" s="11" t="s">
-        <v>33</v>
-      </c>
-      <c r="D4" s="11" t="s">
+      <c r="A4" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="B4" s="8" t="s">
         <v>5</v>
       </c>
-      <c r="E4" s="11" t="s">
+      <c r="C4" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="D4" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="E4" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="F4" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="G4" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="H4" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="I4" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="J4" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="K4" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="L4" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="M4" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="N4" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="O4" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="P4" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="Q4" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="R4" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="S4" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="T4" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="U4" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="F4" s="11" t="s">
-        <v>6</v>
-      </c>
-      <c r="G4" s="11" t="s">
-        <v>35</v>
-      </c>
-      <c r="H4" s="11" t="s">
+      <c r="V4" s="8" t="s">
         <v>36</v>
       </c>
-      <c r="I4" s="11" t="s">
-        <v>9</v>
-      </c>
-      <c r="J4" s="11" t="s">
-        <v>10</v>
-      </c>
-      <c r="K4" s="11" t="s">
-        <v>11</v>
-      </c>
-      <c r="L4" s="11" t="s">
+      <c r="W4" s="8" t="s">
+        <v>38</v>
+      </c>
+      <c r="X4" s="8" t="s">
+        <v>39</v>
+      </c>
+      <c r="Y4" s="8" t="s">
+        <v>40</v>
+      </c>
+      <c r="Z4" s="8" t="s">
+        <v>42</v>
+      </c>
+      <c r="AA4" s="8" t="s">
+        <v>43</v>
+      </c>
+      <c r="AB4" s="8" t="s">
+        <v>44</v>
+      </c>
+      <c r="AC4" s="8" t="s">
+        <v>45</v>
+      </c>
+      <c r="AD4" s="11" t="s">
+        <v>90</v>
+      </c>
+      <c r="AE4" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="AF4" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="AG4" s="8" t="s">
         <v>37</v>
       </c>
-      <c r="M4" s="11" t="s">
-        <v>38</v>
-      </c>
-      <c r="N4" s="11" t="s">
-        <v>39</v>
-      </c>
-      <c r="O4" s="11" t="s">
-        <v>12</v>
-      </c>
-      <c r="P4" s="11" t="s">
-        <v>13</v>
-      </c>
-      <c r="Q4" s="11" t="s">
-        <v>14</v>
-      </c>
-      <c r="R4" s="11" t="s">
-        <v>16</v>
-      </c>
-      <c r="S4" s="11" t="s">
-        <v>17</v>
-      </c>
-      <c r="T4" s="11" t="s">
-        <v>18</v>
-      </c>
-      <c r="U4" s="11" t="s">
-        <v>43</v>
-      </c>
-      <c r="V4" s="11" t="s">
-        <v>44</v>
-      </c>
-      <c r="W4" s="11" t="s">
-        <v>45</v>
-      </c>
-      <c r="X4" s="11" t="s">
-        <v>46</v>
-      </c>
-      <c r="Y4" s="11" t="s">
-        <v>47</v>
-      </c>
-      <c r="Z4" s="11" t="s">
-        <v>48</v>
-      </c>
-      <c r="AA4" s="11" t="s">
-        <v>51</v>
-      </c>
-      <c r="AB4" s="11" t="s">
-        <v>52</v>
-      </c>
-      <c r="AC4" s="11" t="s">
+      <c r="AH4" s="8" t="s">
         <v>53</v>
       </c>
-      <c r="AD4" s="14" t="s">
-        <v>95</v>
-      </c>
-      <c r="AE4" s="11" t="s">
-        <v>19</v>
-      </c>
-      <c r="AF4" s="11" t="s">
-        <v>20</v>
-      </c>
-      <c r="AG4" s="11" t="s">
-        <v>28</v>
-      </c>
-      <c r="AH4" s="11" t="s">
-        <v>57</v>
-      </c>
-      <c r="AI4" s="11" t="s">
+      <c r="AI4" s="8" t="s">
+        <v>91</v>
+      </c>
+      <c r="AJ4" s="6"/>
+      <c r="AK4" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="AL4" s="8" t="s">
+        <v>93</v>
+      </c>
+      <c r="AM4" s="8" t="s">
+        <v>94</v>
+      </c>
+      <c r="AN4" s="8" t="s">
         <v>96</v>
       </c>
-      <c r="AJ4" s="6"/>
-      <c r="AK4" s="11" t="s">
-        <v>3</v>
-      </c>
-      <c r="AL4" s="11" t="s">
+      <c r="AO4" s="8" t="s">
         <v>98</v>
       </c>
-      <c r="AM4" s="11" t="s">
+      <c r="AP4" s="8" t="s">
+        <v>99</v>
+      </c>
+      <c r="AQ4" s="8" t="s">
         <v>100</v>
       </c>
-      <c r="AN4" s="11" t="s">
+      <c r="AR4" s="6"/>
+      <c r="AS4" s="8" t="s">
+        <v>63</v>
+      </c>
+      <c r="AT4" s="8" t="s">
+        <v>93</v>
+      </c>
+      <c r="AU4" s="8" t="s">
         <v>101</v>
       </c>
-      <c r="AO4" s="11" t="s">
-        <v>102</v>
-      </c>
-      <c r="AP4" s="11" t="s">
+      <c r="AV4" s="8" t="s">
+        <v>66</v>
+      </c>
+      <c r="AW4" s="8" t="s">
+        <v>67</v>
+      </c>
+      <c r="AX4" s="8" t="s">
+        <v>68</v>
+      </c>
+      <c r="AY4" s="6"/>
+      <c r="AZ4" s="8" t="s">
         <v>103</v>
       </c>
-      <c r="AQ4" s="11" t="s">
+      <c r="BA4" s="8" t="s">
         <v>104</v>
-      </c>
-      <c r="AR4" s="6"/>
-      <c r="AS4" s="11" t="s">
-        <v>66</v>
-      </c>
-      <c r="AT4" s="11" t="s">
-        <v>98</v>
-      </c>
-      <c r="AU4" s="11" t="s">
-        <v>105</v>
-      </c>
-      <c r="AV4" s="11" t="s">
-        <v>71</v>
-      </c>
-      <c r="AW4" s="11" t="s">
-        <v>72</v>
-      </c>
-      <c r="AX4" s="11" t="s">
-        <v>73</v>
-      </c>
-      <c r="AY4" s="6"/>
-      <c r="AZ4" s="11" t="s">
-        <v>106</v>
-      </c>
-      <c r="BA4" s="11" t="s">
-        <v>107</v>
       </c>
     </row>
     <row r="5">
@@ -7414,16 +7414,16 @@
         <v>61.0</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>31</v>
+        <v>47</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>32</v>
+        <v>48</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="F5" s="3">
         <v>1.0</v>
@@ -7440,7 +7440,7 @@
       <c r="J5" s="3">
         <v>21.0</v>
       </c>
-      <c r="K5" s="15">
+      <c r="K5" s="13">
         <v>0.524</v>
       </c>
       <c r="L5" s="3">
@@ -7449,7 +7449,7 @@
       <c r="M5" s="3">
         <v>12.0</v>
       </c>
-      <c r="N5" s="15">
+      <c r="N5" s="13">
         <v>0.417</v>
       </c>
       <c r="O5" s="3">
@@ -7458,7 +7458,7 @@
       <c r="P5" s="3">
         <v>9.0</v>
       </c>
-      <c r="Q5" s="15">
+      <c r="Q5" s="13">
         <v>0.667</v>
       </c>
       <c r="R5" s="3">
@@ -7467,7 +7467,7 @@
       <c r="S5" s="3">
         <v>0.0</v>
       </c>
-      <c r="T5" s="15">
+      <c r="T5" s="13">
         <v>0.0</v>
       </c>
       <c r="U5" s="3">
@@ -7500,25 +7500,25 @@
       <c r="AD5" s="3">
         <v>-2.0</v>
       </c>
-      <c r="AE5" s="15">
+      <c r="AE5" s="13">
         <v>0.667</v>
       </c>
-      <c r="AF5" s="15">
+      <c r="AF5" s="13">
         <v>0.667</v>
       </c>
       <c r="AG5" s="3">
         <v>3.0</v>
       </c>
       <c r="AH5" s="3" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="AI5" s="3" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="AK5" s="3" t="s">
-        <v>115</v>
-      </c>
-      <c r="AL5" s="13">
+        <v>118</v>
+      </c>
+      <c r="AL5" s="12">
         <v>0.5159722222222223</v>
       </c>
       <c r="AM5" s="3">
@@ -7527,22 +7527,22 @@
       <c r="AN5" s="3">
         <v>99.0</v>
       </c>
-      <c r="AO5" s="8">
+      <c r="AO5" s="9">
         <v>9.5</v>
       </c>
       <c r="AP5" s="3">
         <v>-9.5</v>
       </c>
-      <c r="AQ5" s="8">
+      <c r="AQ5" s="9">
         <v>19</v>
       </c>
       <c r="AS5" s="3" t="s">
         <v>120</v>
       </c>
-      <c r="AT5" s="13">
+      <c r="AT5" s="12">
         <v>0.3541666666666667</v>
       </c>
-      <c r="AU5" s="8">
+      <c r="AU5" s="9">
         <v>6</v>
       </c>
       <c r="AV5" s="3">
@@ -7551,14 +7551,14 @@
       <c r="AW5" s="3">
         <v>100.0</v>
       </c>
-      <c r="AX5" s="8">
+      <c r="AX5" s="9">
         <v>14.5</v>
       </c>
       <c r="AZ5" s="3" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="BA5" s="3" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
     </row>
     <row r="6">
@@ -7566,21 +7566,21 @@
         <v>28.0</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>31</v>
+        <v>47</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="F6" s="3">
         <v>1.0</v>
       </c>
-      <c r="G6" s="13">
+      <c r="G6" s="12">
         <v>0.9576388888888889</v>
       </c>
       <c r="H6" s="3">
@@ -7592,7 +7592,7 @@
       <c r="J6" s="3">
         <v>8.0</v>
       </c>
-      <c r="K6" s="15">
+      <c r="K6" s="13">
         <v>0.5</v>
       </c>
       <c r="L6" s="3">
@@ -7601,7 +7601,7 @@
       <c r="M6" s="3">
         <v>2.0</v>
       </c>
-      <c r="N6" s="15">
+      <c r="N6" s="13">
         <v>1.0</v>
       </c>
       <c r="O6" s="3">
@@ -7610,7 +7610,7 @@
       <c r="P6" s="3">
         <v>6.0</v>
       </c>
-      <c r="Q6" s="15">
+      <c r="Q6" s="13">
         <v>0.333</v>
       </c>
       <c r="R6" s="3">
@@ -7619,7 +7619,7 @@
       <c r="S6" s="3">
         <v>6.0</v>
       </c>
-      <c r="T6" s="15">
+      <c r="T6" s="13">
         <v>1.0</v>
       </c>
       <c r="U6" s="3">
@@ -7652,25 +7652,25 @@
       <c r="AD6" s="3">
         <v>-1.0</v>
       </c>
-      <c r="AE6" s="15">
+      <c r="AE6" s="13">
         <v>0.625</v>
       </c>
-      <c r="AF6" s="15">
+      <c r="AF6" s="13">
         <v>0.752</v>
       </c>
       <c r="AG6" s="3">
         <v>0.0</v>
       </c>
       <c r="AH6" s="3" t="s">
-        <v>117</v>
+        <v>129</v>
       </c>
       <c r="AI6" s="3" t="s">
-        <v>130</v>
+        <v>138</v>
       </c>
       <c r="AK6" s="3" t="s">
-        <v>131</v>
-      </c>
-      <c r="AL6" s="13">
+        <v>139</v>
+      </c>
+      <c r="AL6" s="12">
         <v>0.15069444444444444</v>
       </c>
       <c r="AM6" s="3">
@@ -7679,22 +7679,22 @@
       <c r="AN6" s="3">
         <v>100.5</v>
       </c>
-      <c r="AO6" s="8">
+      <c r="AO6" s="9">
         <v>5.5</v>
       </c>
       <c r="AP6" s="3">
         <v>-7.0</v>
       </c>
-      <c r="AQ6" s="8">
+      <c r="AQ6" s="9">
         <v>12.5</v>
       </c>
       <c r="AS6" s="3" t="s">
-        <v>132</v>
-      </c>
-      <c r="AT6" s="13">
+        <v>143</v>
+      </c>
+      <c r="AT6" s="12">
         <v>0.28125</v>
       </c>
-      <c r="AU6" s="8">
+      <c r="AU6" s="9">
         <v>5</v>
       </c>
       <c r="AV6" s="3">
@@ -7703,14 +7703,14 @@
       <c r="AW6" s="3">
         <v>101.5</v>
       </c>
-      <c r="AX6" s="8">
+      <c r="AX6" s="9">
         <v>10.5</v>
       </c>
       <c r="AZ6" s="3" t="s">
-        <v>133</v>
+        <v>149</v>
       </c>
       <c r="BA6" s="3" t="s">
-        <v>134</v>
+        <v>150</v>
       </c>
     </row>
     <row r="7">
@@ -7718,16 +7718,16 @@
         <v>17.0</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>135</v>
+        <v>140</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>31</v>
+        <v>47</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>136</v>
+        <v>142</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="F7" s="3">
         <v>1.0</v>
@@ -7744,7 +7744,7 @@
       <c r="J7" s="3">
         <v>9.0</v>
       </c>
-      <c r="K7" s="15">
+      <c r="K7" s="13">
         <v>0.333</v>
       </c>
       <c r="L7" s="3">
@@ -7753,7 +7753,7 @@
       <c r="M7" s="3">
         <v>3.0</v>
       </c>
-      <c r="N7" s="15">
+      <c r="N7" s="13">
         <v>0.333</v>
       </c>
       <c r="O7" s="3">
@@ -7762,7 +7762,7 @@
       <c r="P7" s="3">
         <v>6.0</v>
       </c>
-      <c r="Q7" s="15">
+      <c r="Q7" s="13">
         <v>0.333</v>
       </c>
       <c r="R7" s="3">
@@ -7771,7 +7771,7 @@
       <c r="S7" s="3">
         <v>6.0</v>
       </c>
-      <c r="T7" s="15">
+      <c r="T7" s="13">
         <v>0.833</v>
       </c>
       <c r="U7" s="3">
@@ -7804,23 +7804,23 @@
       <c r="AD7" s="3">
         <v>-2.0</v>
       </c>
-      <c r="AE7" s="15">
+      <c r="AE7" s="13">
         <v>0.444</v>
       </c>
-      <c r="AF7" s="15">
+      <c r="AF7" s="13">
         <v>0.558</v>
       </c>
       <c r="AG7" s="3">
         <v>0.0</v>
       </c>
       <c r="AH7" s="3" t="s">
-        <v>140</v>
+        <v>154</v>
       </c>
       <c r="AI7" s="3" t="s">
-        <v>141</v>
+        <v>155</v>
       </c>
       <c r="AK7" s="3" t="s">
-        <v>92</v>
+        <v>87</v>
       </c>
       <c r="AL7" s="7">
         <v>1.3006944444444444</v>
@@ -7837,13 +7837,13 @@
       <c r="AP7" s="3">
         <v>-14.5</v>
       </c>
-      <c r="AQ7" s="8">
+      <c r="AQ7" s="9">
         <v>13.5</v>
       </c>
       <c r="AS7" s="3" t="s">
-        <v>142</v>
-      </c>
-      <c r="AT7" s="13">
+        <v>160</v>
+      </c>
+      <c r="AT7" s="12">
         <v>0.3020833333333333</v>
       </c>
       <c r="AU7" s="3">
@@ -7859,10 +7859,10 @@
         <v>-34.0</v>
       </c>
       <c r="AZ7" s="3" t="s">
-        <v>143</v>
+        <v>152</v>
       </c>
       <c r="BA7" s="3" t="s">
-        <v>144</v>
+        <v>162</v>
       </c>
     </row>
     <row r="8">
@@ -7870,21 +7870,21 @@
         <v>20.0</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>145</v>
+        <v>161</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>31</v>
+        <v>47</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>136</v>
+        <v>142</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="F8" s="3">
         <v>1.0</v>
       </c>
-      <c r="G8" s="13">
+      <c r="G8" s="12">
         <v>0.7541666666666667</v>
       </c>
       <c r="H8" s="3">
@@ -7896,7 +7896,7 @@
       <c r="J8" s="3">
         <v>12.0</v>
       </c>
-      <c r="K8" s="15">
+      <c r="K8" s="13">
         <v>0.333</v>
       </c>
       <c r="L8" s="3">
@@ -7905,7 +7905,7 @@
       <c r="M8" s="3">
         <v>4.0</v>
       </c>
-      <c r="N8" s="15">
+      <c r="N8" s="13">
         <v>0.25</v>
       </c>
       <c r="O8" s="3">
@@ -7914,7 +7914,7 @@
       <c r="P8" s="3">
         <v>8.0</v>
       </c>
-      <c r="Q8" s="15">
+      <c r="Q8" s="13">
         <v>0.375</v>
       </c>
       <c r="R8" s="3">
@@ -7923,7 +7923,7 @@
       <c r="S8" s="3">
         <v>2.0</v>
       </c>
-      <c r="T8" s="15">
+      <c r="T8" s="13">
         <v>0.5</v>
       </c>
       <c r="U8" s="3">
@@ -7956,25 +7956,25 @@
       <c r="AD8" s="3">
         <v>-4.0</v>
       </c>
-      <c r="AE8" s="15">
+      <c r="AE8" s="13">
         <v>0.458</v>
       </c>
-      <c r="AF8" s="15">
+      <c r="AF8" s="13">
         <v>0.466</v>
       </c>
       <c r="AG8" s="3">
         <v>0.0</v>
       </c>
       <c r="AH8" s="3" t="s">
-        <v>146</v>
+        <v>113</v>
       </c>
       <c r="AI8" s="3" t="s">
-        <v>147</v>
+        <v>163</v>
       </c>
       <c r="AK8" s="3" t="s">
-        <v>148</v>
-      </c>
-      <c r="AL8" s="13">
+        <v>165</v>
+      </c>
+      <c r="AL8" s="12">
         <v>0.9576388888888889</v>
       </c>
       <c r="AM8" s="3">
@@ -7989,7 +7989,7 @@
       <c r="AP8" s="3">
         <v>-6.5</v>
       </c>
-      <c r="AQ8" s="8">
+      <c r="AQ8" s="9">
         <v>3.5</v>
       </c>
     </row>
@@ -7998,21 +7998,21 @@
         <v>0.0</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>59</v>
+        <v>76</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>41</v>
+        <v>50</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>150</v>
+        <v>169</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>99</v>
+        <v>107</v>
       </c>
       <c r="F9" s="3">
         <v>1.0</v>
       </c>
-      <c r="G9" s="13">
+      <c r="G9" s="12">
         <v>0.15069444444444444</v>
       </c>
       <c r="H9" s="3">
@@ -8024,7 +8024,7 @@
       <c r="J9" s="3">
         <v>10.0</v>
       </c>
-      <c r="K9" s="15">
+      <c r="K9" s="13">
         <v>0.2</v>
       </c>
       <c r="L9" s="3">
@@ -8033,7 +8033,7 @@
       <c r="M9" s="3">
         <v>5.0</v>
       </c>
-      <c r="N9" s="15">
+      <c r="N9" s="13">
         <v>0.4</v>
       </c>
       <c r="O9" s="3">
@@ -8042,7 +8042,7 @@
       <c r="P9" s="3">
         <v>5.0</v>
       </c>
-      <c r="Q9" s="15">
+      <c r="Q9" s="13">
         <v>0.0</v>
       </c>
       <c r="R9" s="3">
@@ -8051,7 +8051,7 @@
       <c r="S9" s="3">
         <v>4.0</v>
       </c>
-      <c r="T9" s="15">
+      <c r="T9" s="13">
         <v>0.5</v>
       </c>
       <c r="U9" s="3">
@@ -8081,26 +8081,26 @@
       <c r="AC9" s="3">
         <v>5.0</v>
       </c>
-      <c r="AD9" s="8">
+      <c r="AD9" s="9">
         <v>5</v>
       </c>
-      <c r="AE9" s="15">
+      <c r="AE9" s="13">
         <v>0.2</v>
       </c>
-      <c r="AF9" s="15">
+      <c r="AF9" s="13">
         <v>0.34</v>
       </c>
       <c r="AG9" s="3">
         <v>2.0</v>
       </c>
       <c r="AH9" s="3" t="s">
-        <v>153</v>
+        <v>171</v>
       </c>
       <c r="AI9" s="3" t="s">
-        <v>154</v>
+        <v>172</v>
       </c>
       <c r="AK9" s="3" t="s">
-        <v>156</v>
+        <v>173</v>
       </c>
       <c r="AL9" s="7">
         <v>1.30625</v>
@@ -8126,21 +8126,21 @@
         <v>10.0</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>40</v>
+        <v>49</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>41</v>
+        <v>50</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>42</v>
+        <v>51</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>99</v>
+        <v>107</v>
       </c>
       <c r="F10" s="3">
         <v>1.0</v>
       </c>
-      <c r="G10" s="13">
+      <c r="G10" s="12">
         <v>0.8298611111111112</v>
       </c>
       <c r="H10" s="3">
@@ -8152,7 +8152,7 @@
       <c r="J10" s="3">
         <v>7.0</v>
       </c>
-      <c r="K10" s="15">
+      <c r="K10" s="13">
         <v>0.286</v>
       </c>
       <c r="L10" s="3">
@@ -8161,7 +8161,7 @@
       <c r="M10" s="3">
         <v>1.0</v>
       </c>
-      <c r="N10" s="15">
+      <c r="N10" s="13">
         <v>1.0</v>
       </c>
       <c r="O10" s="3">
@@ -8170,7 +8170,7 @@
       <c r="P10" s="3">
         <v>6.0</v>
       </c>
-      <c r="Q10" s="15">
+      <c r="Q10" s="13">
         <v>0.167</v>
       </c>
       <c r="R10" s="3">
@@ -8179,7 +8179,7 @@
       <c r="S10" s="3">
         <v>0.0</v>
       </c>
-      <c r="T10" s="15">
+      <c r="T10" s="13">
         <v>0.0</v>
       </c>
       <c r="U10" s="3">
@@ -8212,25 +8212,25 @@
       <c r="AD10" s="3">
         <v>-13.0</v>
       </c>
-      <c r="AE10" s="15">
+      <c r="AE10" s="13">
         <v>0.357</v>
       </c>
-      <c r="AF10" s="15">
+      <c r="AF10" s="13">
         <v>0.357</v>
       </c>
       <c r="AG10" s="3">
         <v>0.0</v>
       </c>
       <c r="AH10" s="3" t="s">
-        <v>157</v>
+        <v>178</v>
       </c>
       <c r="AI10" s="3" t="s">
-        <v>158</v>
+        <v>179</v>
       </c>
       <c r="AK10" s="3" t="s">
-        <v>152</v>
-      </c>
-      <c r="AL10" s="13">
+        <v>116</v>
+      </c>
+      <c r="AL10" s="12">
         <v>0.7541666666666667</v>
       </c>
       <c r="AM10" s="3">
@@ -8254,21 +8254,21 @@
         <v>24.0</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>159</v>
+        <v>180</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>41</v>
+        <v>50</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>91</v>
+        <v>109</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>161</v>
+        <v>181</v>
       </c>
       <c r="F11" s="3">
         <v>1.0</v>
       </c>
-      <c r="G11" s="13">
+      <c r="G11" s="12">
         <v>0.5159722222222223</v>
       </c>
       <c r="H11" s="3">
@@ -8280,7 +8280,7 @@
       <c r="J11" s="3">
         <v>3.0</v>
       </c>
-      <c r="K11" s="15">
+      <c r="K11" s="13">
         <v>0.333</v>
       </c>
       <c r="L11" s="3">
@@ -8289,7 +8289,7 @@
       <c r="M11" s="3">
         <v>1.0</v>
       </c>
-      <c r="N11" s="15">
+      <c r="N11" s="13">
         <v>0.0</v>
       </c>
       <c r="O11" s="3">
@@ -8298,7 +8298,7 @@
       <c r="P11" s="3">
         <v>2.0</v>
       </c>
-      <c r="Q11" s="15">
+      <c r="Q11" s="13">
         <v>0.5</v>
       </c>
       <c r="R11" s="3">
@@ -8307,7 +8307,7 @@
       <c r="S11" s="3">
         <v>0.0</v>
       </c>
-      <c r="T11" s="15">
+      <c r="T11" s="13">
         <v>0.0</v>
       </c>
       <c r="U11" s="3">
@@ -8337,28 +8337,28 @@
       <c r="AC11" s="3">
         <v>8.0</v>
       </c>
-      <c r="AD11" s="8">
+      <c r="AD11" s="9">
         <v>8</v>
       </c>
-      <c r="AE11" s="15">
-        <v>0.5</v>
-      </c>
-      <c r="AF11" s="15">
+      <c r="AE11" s="13">
+        <v>0.5</v>
+      </c>
+      <c r="AF11" s="13">
         <v>0.5</v>
       </c>
       <c r="AG11" s="3">
         <v>0.0</v>
       </c>
       <c r="AH11" s="3" t="s">
-        <v>163</v>
+        <v>185</v>
       </c>
       <c r="AI11" s="3" t="s">
-        <v>164</v>
+        <v>186</v>
       </c>
       <c r="AK11" s="3" t="s">
-        <v>119</v>
-      </c>
-      <c r="AL11" s="13">
+        <v>132</v>
+      </c>
+      <c r="AL11" s="12">
         <v>0.8201388888888889</v>
       </c>
       <c r="AM11" s="3">
@@ -8370,7 +8370,7 @@
       <c r="AO11" s="3">
         <v>-11.5</v>
       </c>
-      <c r="AP11" s="8">
+      <c r="AP11" s="9">
         <v>2</v>
       </c>
       <c r="AQ11" s="3">
@@ -8382,21 +8382,21 @@
         <v>7.0</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>55</v>
+        <v>73</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>41</v>
+        <v>50</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>166</v>
+        <v>189</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>99</v>
+        <v>107</v>
       </c>
       <c r="F12" s="3">
         <v>1.0</v>
       </c>
-      <c r="G12" s="13">
+      <c r="G12" s="12">
         <v>0.8201388888888889</v>
       </c>
       <c r="H12" s="3">
@@ -8408,7 +8408,7 @@
       <c r="J12" s="3">
         <v>7.0</v>
       </c>
-      <c r="K12" s="15">
+      <c r="K12" s="13">
         <v>0.0</v>
       </c>
       <c r="L12" s="3">
@@ -8417,7 +8417,7 @@
       <c r="M12" s="3">
         <v>5.0</v>
       </c>
-      <c r="N12" s="15">
+      <c r="N12" s="13">
         <v>0.0</v>
       </c>
       <c r="O12" s="3">
@@ -8426,7 +8426,7 @@
       <c r="P12" s="3">
         <v>2.0</v>
       </c>
-      <c r="Q12" s="15">
+      <c r="Q12" s="13">
         <v>0.0</v>
       </c>
       <c r="R12" s="3">
@@ -8435,7 +8435,7 @@
       <c r="S12" s="3">
         <v>2.0</v>
       </c>
-      <c r="T12" s="15">
+      <c r="T12" s="13">
         <v>0.5</v>
       </c>
       <c r="U12" s="3">
@@ -8468,25 +8468,25 @@
       <c r="AD12" s="3">
         <v>-8.0</v>
       </c>
-      <c r="AE12" s="15">
-        <v>0.0</v>
-      </c>
-      <c r="AF12" s="15">
+      <c r="AE12" s="13">
+        <v>0.0</v>
+      </c>
+      <c r="AF12" s="13">
         <v>0.19</v>
       </c>
       <c r="AG12" s="3">
         <v>9.0</v>
       </c>
       <c r="AH12" s="3" t="s">
-        <v>167</v>
+        <v>190</v>
       </c>
       <c r="AI12" s="3" t="s">
-        <v>168</v>
+        <v>191</v>
       </c>
       <c r="AK12" s="3" t="s">
-        <v>110</v>
-      </c>
-      <c r="AL12" s="13">
+        <v>112</v>
+      </c>
+      <c r="AL12" s="12">
         <v>0.8298611111111112</v>
       </c>
       <c r="AM12" s="3">
@@ -8498,7 +8498,7 @@
       <c r="AO12" s="3">
         <v>-17.5</v>
       </c>
-      <c r="AP12" s="8">
+      <c r="AP12" s="9">
         <v>5.5</v>
       </c>
       <c r="AQ12" s="3">
@@ -8510,21 +8510,21 @@
         <v>12.0</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>171</v>
+        <v>192</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>41</v>
+        <v>50</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>32</v>
+        <v>48</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>172</v>
+        <v>195</v>
       </c>
       <c r="F13" s="3">
         <v>1.0</v>
       </c>
-      <c r="G13" s="13">
+      <c r="G13" s="12">
         <v>0.32222222222222224</v>
       </c>
       <c r="H13" s="3">
@@ -8536,7 +8536,7 @@
       <c r="J13" s="3">
         <v>2.0</v>
       </c>
-      <c r="K13" s="15">
+      <c r="K13" s="13">
         <v>0.5</v>
       </c>
       <c r="L13" s="3">
@@ -8545,7 +8545,7 @@
       <c r="M13" s="3">
         <v>2.0</v>
       </c>
-      <c r="N13" s="15">
+      <c r="N13" s="13">
         <v>0.5</v>
       </c>
       <c r="O13" s="3">
@@ -8554,7 +8554,7 @@
       <c r="P13" s="3">
         <v>0.0</v>
       </c>
-      <c r="Q13" s="15">
+      <c r="Q13" s="13">
         <v>0.0</v>
       </c>
       <c r="R13" s="3">
@@ -8563,7 +8563,7 @@
       <c r="S13" s="3">
         <v>2.0</v>
       </c>
-      <c r="T13" s="15">
+      <c r="T13" s="13">
         <v>0.0</v>
       </c>
       <c r="U13" s="3">
@@ -8593,23 +8593,23 @@
       <c r="AC13" s="3">
         <v>0.0</v>
       </c>
-      <c r="AD13" s="8">
+      <c r="AD13" s="9">
         <v>8</v>
       </c>
-      <c r="AE13" s="15">
-        <v>0.5</v>
-      </c>
-      <c r="AF13" s="15">
+      <c r="AE13" s="13">
+        <v>0.5</v>
+      </c>
+      <c r="AF13" s="13">
         <v>0.347</v>
       </c>
       <c r="AG13" s="3">
         <v>0.0</v>
       </c>
       <c r="AH13" s="3" t="s">
-        <v>174</v>
+        <v>198</v>
       </c>
       <c r="AI13" s="3" t="s">
-        <v>175</v>
+        <v>199</v>
       </c>
     </row>
     <row r="14">
@@ -8617,21 +8617,21 @@
         <v>77.0</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>176</v>
+        <v>197</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>41</v>
+        <v>50</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>91</v>
+        <v>109</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>161</v>
+        <v>181</v>
       </c>
       <c r="F14" s="3">
         <v>1.0</v>
       </c>
-      <c r="G14" s="13">
+      <c r="G14" s="12">
         <v>0.15625</v>
       </c>
       <c r="H14" s="3">
@@ -8643,7 +8643,7 @@
       <c r="J14" s="3">
         <v>1.0</v>
       </c>
-      <c r="K14" s="15">
+      <c r="K14" s="13">
         <v>0.0</v>
       </c>
       <c r="L14" s="3">
@@ -8652,7 +8652,7 @@
       <c r="M14" s="3">
         <v>0.0</v>
       </c>
-      <c r="N14" s="15">
+      <c r="N14" s="13">
         <v>0.0</v>
       </c>
       <c r="O14" s="3">
@@ -8661,7 +8661,7 @@
       <c r="P14" s="3">
         <v>1.0</v>
       </c>
-      <c r="Q14" s="15">
+      <c r="Q14" s="13">
         <v>0.0</v>
       </c>
       <c r="R14" s="3">
@@ -8670,7 +8670,7 @@
       <c r="S14" s="3">
         <v>0.0</v>
       </c>
-      <c r="T14" s="15">
+      <c r="T14" s="13">
         <v>0.0</v>
       </c>
       <c r="U14" s="3">
@@ -8703,20 +8703,20 @@
       <c r="AD14" s="3">
         <v>-2.0</v>
       </c>
-      <c r="AE14" s="15">
-        <v>0.0</v>
-      </c>
-      <c r="AF14" s="15">
+      <c r="AE14" s="13">
+        <v>0.0</v>
+      </c>
+      <c r="AF14" s="13">
         <v>0.0</v>
       </c>
       <c r="AG14" s="3">
         <v>0.0</v>
       </c>
       <c r="AH14" s="3" t="s">
-        <v>179</v>
+        <v>202</v>
       </c>
       <c r="AI14" s="3" t="s">
-        <v>180</v>
+        <v>203</v>
       </c>
     </row>
     <row r="15">
@@ -8724,21 +8724,21 @@
         <v>76.0</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>80</v>
+        <v>86</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>41</v>
+        <v>50</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>173</v>
+        <v>196</v>
       </c>
       <c r="F15" s="3">
         <v>1.0</v>
       </c>
-      <c r="G15" s="13">
+      <c r="G15" s="12">
         <v>0.6555555555555556</v>
       </c>
       <c r="H15" s="3">
@@ -8750,7 +8750,7 @@
       <c r="J15" s="3">
         <v>1.0</v>
       </c>
-      <c r="K15" s="15">
+      <c r="K15" s="13">
         <v>0.0</v>
       </c>
       <c r="L15" s="3">
@@ -8759,7 +8759,7 @@
       <c r="M15" s="3">
         <v>0.0</v>
       </c>
-      <c r="N15" s="15">
+      <c r="N15" s="13">
         <v>0.0</v>
       </c>
       <c r="O15" s="3">
@@ -8768,7 +8768,7 @@
       <c r="P15" s="3">
         <v>1.0</v>
       </c>
-      <c r="Q15" s="15">
+      <c r="Q15" s="13">
         <v>0.0</v>
       </c>
       <c r="R15" s="3">
@@ -8777,7 +8777,7 @@
       <c r="S15" s="3">
         <v>0.0</v>
       </c>
-      <c r="T15" s="15">
+      <c r="T15" s="13">
         <v>0.0</v>
       </c>
       <c r="U15" s="3">
@@ -8810,20 +8810,20 @@
       <c r="AD15" s="3">
         <v>0.0</v>
       </c>
-      <c r="AE15" s="15">
-        <v>0.0</v>
-      </c>
-      <c r="AF15" s="15">
+      <c r="AE15" s="13">
+        <v>0.0</v>
+      </c>
+      <c r="AF15" s="13">
         <v>0.0</v>
       </c>
       <c r="AG15" s="3">
         <v>0.0</v>
       </c>
       <c r="AH15" s="3" t="s">
-        <v>182</v>
+        <v>206</v>
       </c>
       <c r="AI15" s="3" t="s">
-        <v>183</v>
+        <v>207</v>
       </c>
     </row>
     <row r="16">
@@ -8831,21 +8831,21 @@
         <v>1.0</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>186</v>
+        <v>209</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>41</v>
+        <v>50</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>32</v>
+        <v>48</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>181</v>
+        <v>205</v>
       </c>
       <c r="F16" s="3">
         <v>1.0</v>
       </c>
-      <c r="G16" s="13">
+      <c r="G16" s="12">
         <v>0.15416666666666667</v>
       </c>
       <c r="H16" s="3">
@@ -8857,7 +8857,7 @@
       <c r="J16" s="3">
         <v>0.0</v>
       </c>
-      <c r="K16" s="15">
+      <c r="K16" s="13">
         <v>0.0</v>
       </c>
       <c r="L16" s="3">
@@ -8866,7 +8866,7 @@
       <c r="M16" s="3">
         <v>0.0</v>
       </c>
-      <c r="N16" s="15">
+      <c r="N16" s="13">
         <v>0.0</v>
       </c>
       <c r="O16" s="3">
@@ -8875,7 +8875,7 @@
       <c r="P16" s="3">
         <v>0.0</v>
       </c>
-      <c r="Q16" s="15">
+      <c r="Q16" s="13">
         <v>0.0</v>
       </c>
       <c r="R16" s="3">
@@ -8884,7 +8884,7 @@
       <c r="S16" s="3">
         <v>0.0</v>
       </c>
-      <c r="T16" s="15">
+      <c r="T16" s="13">
         <v>0.0</v>
       </c>
       <c r="U16" s="3">
@@ -8917,20 +8917,20 @@
       <c r="AD16" s="3">
         <v>-4.0</v>
       </c>
-      <c r="AE16" s="15">
-        <v>0.0</v>
-      </c>
-      <c r="AF16" s="15">
+      <c r="AE16" s="13">
+        <v>0.0</v>
+      </c>
+      <c r="AF16" s="13">
         <v>0.0</v>
       </c>
       <c r="AG16" s="3">
         <v>0.0</v>
       </c>
       <c r="AH16" s="3" t="s">
-        <v>187</v>
+        <v>214</v>
       </c>
       <c r="AI16" s="3" t="s">
-        <v>188</v>
+        <v>215</v>
       </c>
     </row>
     <row r="17">
@@ -8938,21 +8938,21 @@
         <v>14.0</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>189</v>
+        <v>213</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>41</v>
+        <v>50</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>32</v>
+        <v>48</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="F17" s="3">
         <v>0.0</v>
       </c>
-      <c r="G17" s="13">
+      <c r="G17" s="12">
         <v>0.0</v>
       </c>
       <c r="H17" s="3">
@@ -8964,7 +8964,7 @@
       <c r="J17" s="3">
         <v>0.0</v>
       </c>
-      <c r="K17" s="15">
+      <c r="K17" s="13">
         <v>0.0</v>
       </c>
       <c r="L17" s="3">
@@ -8973,7 +8973,7 @@
       <c r="M17" s="3">
         <v>0.0</v>
       </c>
-      <c r="N17" s="15">
+      <c r="N17" s="13">
         <v>0.0</v>
       </c>
       <c r="O17" s="3">
@@ -8982,7 +8982,7 @@
       <c r="P17" s="3">
         <v>0.0</v>
       </c>
-      <c r="Q17" s="15">
+      <c r="Q17" s="13">
         <v>0.0</v>
       </c>
       <c r="R17" s="3">
@@ -8991,7 +8991,7 @@
       <c r="S17" s="3">
         <v>0.0</v>
       </c>
-      <c r="T17" s="15">
+      <c r="T17" s="13">
         <v>0.0</v>
       </c>
       <c r="U17" s="3">
@@ -9024,20 +9024,20 @@
       <c r="AD17" s="3">
         <v>0.0</v>
       </c>
-      <c r="AE17" s="15">
-        <v>0.0</v>
-      </c>
-      <c r="AF17" s="15">
+      <c r="AE17" s="13">
+        <v>0.0</v>
+      </c>
+      <c r="AF17" s="13">
         <v>0.0</v>
       </c>
       <c r="AG17" s="3">
         <v>0.0</v>
       </c>
       <c r="AH17" s="3" t="s">
-        <v>192</v>
+        <v>218</v>
       </c>
       <c r="AI17" s="3" t="s">
-        <v>193</v>
+        <v>219</v>
       </c>
     </row>
     <row r="18">
@@ -9045,21 +9045,21 @@
         <v>5.0</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>90</v>
+        <v>108</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>41</v>
+        <v>50</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>91</v>
+        <v>109</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>161</v>
+        <v>181</v>
       </c>
       <c r="F18" s="3">
         <v>0.0</v>
       </c>
-      <c r="G18" s="13">
+      <c r="G18" s="12">
         <v>0.0</v>
       </c>
       <c r="H18" s="3">
@@ -9071,7 +9071,7 @@
       <c r="J18" s="3">
         <v>0.0</v>
       </c>
-      <c r="K18" s="15">
+      <c r="K18" s="13">
         <v>0.0</v>
       </c>
       <c r="L18" s="3">
@@ -9080,7 +9080,7 @@
       <c r="M18" s="3">
         <v>0.0</v>
       </c>
-      <c r="N18" s="15">
+      <c r="N18" s="13">
         <v>0.0</v>
       </c>
       <c r="O18" s="3">
@@ -9089,7 +9089,7 @@
       <c r="P18" s="3">
         <v>0.0</v>
       </c>
-      <c r="Q18" s="15">
+      <c r="Q18" s="13">
         <v>0.0</v>
       </c>
       <c r="R18" s="3">
@@ -9098,7 +9098,7 @@
       <c r="S18" s="3">
         <v>0.0</v>
       </c>
-      <c r="T18" s="15">
+      <c r="T18" s="13">
         <v>0.0</v>
       </c>
       <c r="U18" s="3">
@@ -9131,37 +9131,37 @@
       <c r="AD18" s="3">
         <v>0.0</v>
       </c>
-      <c r="AE18" s="15">
-        <v>0.0</v>
-      </c>
-      <c r="AF18" s="15">
+      <c r="AE18" s="13">
+        <v>0.0</v>
+      </c>
+      <c r="AF18" s="13">
         <v>0.0</v>
       </c>
       <c r="AG18" s="3">
         <v>0.0</v>
       </c>
       <c r="AH18" s="3" t="s">
-        <v>192</v>
+        <v>218</v>
       </c>
       <c r="AI18" s="3" t="s">
-        <v>193</v>
+        <v>219</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="3" t="s">
-        <v>197</v>
+        <v>223</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>198</v>
+        <v>224</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>199</v>
+        <v>225</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>199</v>
+        <v>225</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>199</v>
+        <v>225</v>
       </c>
       <c r="F19" s="3">
         <v>1.0</v>
@@ -9178,7 +9178,7 @@
       <c r="J19" s="3">
         <v>83.0</v>
       </c>
-      <c r="K19" s="15">
+      <c r="K19" s="13">
         <v>0.361</v>
       </c>
       <c r="L19" s="3">
@@ -9187,7 +9187,7 @@
       <c r="M19" s="3">
         <v>37.0</v>
       </c>
-      <c r="N19" s="15">
+      <c r="N19" s="13">
         <v>0.405</v>
       </c>
       <c r="O19" s="3">
@@ -9196,7 +9196,7 @@
       <c r="P19" s="3">
         <v>46.0</v>
       </c>
-      <c r="Q19" s="15">
+      <c r="Q19" s="13">
         <v>0.326</v>
       </c>
       <c r="R19" s="3">
@@ -9205,7 +9205,7 @@
       <c r="S19" s="3">
         <v>24.0</v>
       </c>
-      <c r="T19" s="15">
+      <c r="T19" s="13">
         <v>0.708</v>
       </c>
       <c r="U19" s="3">
@@ -9238,20 +9238,20 @@
       <c r="AD19" s="3">
         <v>-5.0</v>
       </c>
-      <c r="AE19" s="15">
+      <c r="AE19" s="13">
         <v>0.452</v>
       </c>
-      <c r="AF19" s="15">
+      <c r="AF19" s="13">
         <v>0.492</v>
       </c>
       <c r="AG19" s="3">
         <v>3.0</v>
       </c>
       <c r="AH19" s="3" t="s">
-        <v>201</v>
+        <v>227</v>
       </c>
       <c r="AI19" s="3" t="s">
-        <v>203</v>
+        <v>228</v>
       </c>
     </row>
   </sheetData>
